--- a/MaxPain_GEX.xlsx
+++ b/MaxPain_GEX.xlsx
@@ -36,8 +36,8 @@
     <numFmt numFmtId="174" formatCode="\+0.0%;\-0.0%;0.0%"/>
     <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="176" formatCode="yyyy-mm-dd hh:mm"/>
-    <numFmt numFmtId="177" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="178" formatCode="+0.0;-0.0"/>
+    <numFmt numFmtId="177" formatCode="+0.0;-0.0"/>
+    <numFmt numFmtId="178" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -383,7 +383,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -550,7 +550,8 @@
     <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -953,12 +954,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$137</f>
+              <f>'Max Pain Calc'!$A$2:$A$144</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$137</f>
+              <f>'Max Pain Calc'!$B$2:$B$144</f>
             </numRef>
           </val>
         </ser>
@@ -1031,12 +1032,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'GEX Calc'!$A$2:$A$79</f>
+              <f>'GEX Calc'!$A$2:$A$99</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GEX Calc'!$C$2:$C$79</f>
+              <f>'GEX Calc'!$C$2:$C$99</f>
             </numRef>
           </val>
         </ser>
@@ -1384,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>190</v>
+        <v>79</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1393,7 +1394,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>BB1 Week 1 - OCT 2026 (V26)</t>
+          <t>MW1 Week 1 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1410,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>56</v>
+        <v>3</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1418,7 +1419,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46295</v>
+        <v>46297</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1442,7 +1443,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1458,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1466,7 +1467,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>3048</v>
+        <v>3565</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1476,7 +1477,7 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="61">
       <c r="A6" s="2" t="n">
-        <v>3870</v>
+        <v>3805</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
@@ -1490,7 +1491,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>3400</v>
+        <v>2801</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1500,29 +1501,29 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="61">
       <c r="A7" s="2" t="n">
-        <v>3875</v>
+        <v>3820</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="61">
       <c r="A8" s="2" t="n">
-        <v>3900</v>
+        <v>3825</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="61">
       <c r="A9" s="2" t="n">
-        <v>3905</v>
+        <v>3880</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
@@ -1533,95 +1534,95 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="61">
       <c r="A10" s="2" t="n">
-        <v>3920</v>
+        <v>3895</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="61">
       <c r="A11" s="2" t="n">
-        <v>3925</v>
+        <v>3900</v>
       </c>
       <c r="B11" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="61">
       <c r="A12" s="2" t="n">
-        <v>3935</v>
+        <v>3905</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="61">
       <c r="A13" s="2" t="n">
-        <v>3940</v>
+        <v>3915</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="61">
       <c r="A14" s="2" t="n">
-        <v>3950</v>
+        <v>3925</v>
       </c>
       <c r="B14" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="61">
       <c r="A15" s="2" t="n">
-        <v>3965</v>
+        <v>3935</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="61">
       <c r="A16" s="2" t="n">
-        <v>3970</v>
+        <v>3940</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="61">
       <c r="A17" s="2" t="n">
-        <v>3975</v>
+        <v>3950</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="61">
       <c r="A18" s="2" t="n">
-        <v>3980</v>
+        <v>3955</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
@@ -1632,117 +1633,117 @@
     </row>
     <row r="19" ht="15" customHeight="1" s="61">
       <c r="A19" s="2" t="n">
-        <v>3985</v>
+        <v>3960</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="61">
       <c r="A20" s="2" t="n">
-        <v>3990</v>
+        <v>3965</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="61">
       <c r="A21" s="2" t="n">
-        <v>4000</v>
+        <v>3970</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>58</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="61">
       <c r="A22" s="2" t="n">
-        <v>4010</v>
+        <v>3975</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="61">
       <c r="A23" s="2" t="n">
-        <v>4015</v>
+        <v>3980</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="61">
       <c r="A24" s="2" t="n">
-        <v>4020</v>
+        <v>3985</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="61">
       <c r="A25" s="2" t="n">
-        <v>4025</v>
+        <v>3995</v>
       </c>
       <c r="B25" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>46</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="61">
       <c r="A26" s="2" t="n">
-        <v>4030</v>
+        <v>4000</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>15</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="61">
       <c r="A27" s="2" t="n">
-        <v>4035</v>
+        <v>4005</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="61">
       <c r="A28" s="2" t="n">
-        <v>4040</v>
+        <v>4010</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="61">
       <c r="A29" s="2" t="n">
-        <v>4045</v>
+        <v>4015</v>
       </c>
       <c r="B29" s="3" t="n">
         <v>0</v>
@@ -1753,51 +1754,51 @@
     </row>
     <row r="30" ht="15" customHeight="1" s="61">
       <c r="A30" s="2" t="n">
-        <v>4050</v>
+        <v>4020</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="61">
       <c r="A31" s="2" t="n">
-        <v>4055</v>
+        <v>4025</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>3</v>
+        <v>101</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="61">
       <c r="A32" s="2" t="n">
-        <v>4060</v>
+        <v>4030</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="61">
       <c r="A33" s="2" t="n">
-        <v>4065</v>
+        <v>4035</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="61">
       <c r="A34" s="2" t="n">
-        <v>4070</v>
+        <v>4040</v>
       </c>
       <c r="B34" s="3" t="n">
         <v>0</v>
@@ -1808,472 +1809,472 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="61">
       <c r="A35" s="2" t="n">
-        <v>4075</v>
+        <v>4045</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="61">
       <c r="A36" s="2" t="n">
-        <v>4080</v>
+        <v>4050</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>5</v>
+        <v>344</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="61">
       <c r="A37" s="2" t="n">
-        <v>4085</v>
+        <v>4055</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="61">
       <c r="A38" s="2" t="n">
-        <v>4090</v>
+        <v>4060</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>305</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="61">
       <c r="A39" s="2" t="n">
-        <v>4095</v>
+        <v>4065</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="61">
       <c r="A40" s="2" t="n">
-        <v>4100</v>
+        <v>4070</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>82</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="61">
       <c r="A41" s="2" t="n">
-        <v>4105</v>
+        <v>4075</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>7</v>
+        <v>242</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="61">
       <c r="A42" s="2" t="n">
-        <v>4110</v>
+        <v>4080</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>132</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="61">
       <c r="A43" s="2" t="n">
-        <v>4115</v>
+        <v>4085</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>6</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="61">
       <c r="A44" s="2" t="n">
-        <v>4120</v>
+        <v>4090</v>
       </c>
       <c r="B44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>83</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="61">
       <c r="A45" s="2" t="n">
-        <v>4125</v>
+        <v>4095</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>67</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="61">
       <c r="A46" s="2" t="n">
-        <v>4130</v>
+        <v>4100</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>73</v>
+        <v>237</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="61">
       <c r="A47" s="2" t="n">
-        <v>4135</v>
+        <v>4105</v>
       </c>
       <c r="B47" s="3" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="61">
       <c r="A48" s="2" t="n">
-        <v>4140</v>
+        <v>4110</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="61">
       <c r="A49" s="2" t="n">
-        <v>4145</v>
+        <v>4115</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="61">
       <c r="A50" s="2" t="n">
-        <v>4150</v>
+        <v>4120</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>112</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="61">
       <c r="A51" s="2" t="n">
-        <v>4155</v>
+        <v>4125</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="61">
       <c r="A52" s="2" t="n">
-        <v>4160</v>
+        <v>4130</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4165</v>
+        <v>4135</v>
       </c>
       <c r="B53" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="61">
       <c r="A54" s="2" t="n">
-        <v>4170</v>
+        <v>4140</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="61">
       <c r="A55" s="2" t="n">
-        <v>4175</v>
+        <v>4145</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>108</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="61">
       <c r="A56" s="2" t="n">
-        <v>4180</v>
+        <v>4150</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>45</v>
+        <v>153</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4185</v>
+        <v>4155</v>
       </c>
       <c r="B57" s="3" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4190</v>
+        <v>4160</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4195</v>
+        <v>4165</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4200</v>
+        <v>4170</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>208</v>
+        <v>56</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>247</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4205</v>
+        <v>4175</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4210</v>
+        <v>4180</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>77</v>
+        <v>9</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4215</v>
+        <v>4185</v>
       </c>
       <c r="B63" t="n">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4220</v>
+        <v>4190</v>
       </c>
       <c r="B64" t="n">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="C64" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4225</v>
+        <v>4195</v>
       </c>
       <c r="B65" t="n">
-        <v>111</v>
+        <v>46</v>
       </c>
       <c r="C65" t="n">
-        <v>295</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4230</v>
+        <v>4200</v>
       </c>
       <c r="B66" t="n">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="C66" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4235</v>
+        <v>4205</v>
       </c>
       <c r="B67" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C67" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4240</v>
+        <v>4210</v>
       </c>
       <c r="B68" t="n">
-        <v>45</v>
+        <v>81</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4245</v>
+        <v>4215</v>
       </c>
       <c r="B69" t="n">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="C69" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4250</v>
+        <v>4220</v>
       </c>
       <c r="B70" t="n">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="C70" t="n">
-        <v>202</v>
+        <v>23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4255</v>
+        <v>4225</v>
       </c>
       <c r="B71" t="n">
-        <v>54</v>
+        <v>161</v>
       </c>
       <c r="C71" t="n">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4260</v>
+        <v>4230</v>
       </c>
       <c r="B72" t="n">
         <v>52</v>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4265</v>
+        <v>4235</v>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="C73" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4270</v>
+        <v>4240</v>
       </c>
       <c r="B74" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="C74" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4275</v>
+        <v>4245</v>
       </c>
       <c r="B75" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C75" t="n">
-        <v>98</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4280</v>
+        <v>4250</v>
       </c>
       <c r="B76" t="n">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4285</v>
+        <v>4255</v>
       </c>
       <c r="B77" t="n">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -2281,54 +2282,54 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4290</v>
+        <v>4260</v>
       </c>
       <c r="B78" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4295</v>
+        <v>4265</v>
       </c>
       <c r="B79" t="n">
-        <v>43</v>
+        <v>3</v>
       </c>
       <c r="C79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4300</v>
+        <v>4270</v>
       </c>
       <c r="B80" t="n">
-        <v>118</v>
+        <v>21</v>
       </c>
       <c r="C80" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4305</v>
+        <v>4275</v>
       </c>
       <c r="B81" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="C81" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4310</v>
+        <v>4280</v>
       </c>
       <c r="B82" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -2336,10 +2337,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4315</v>
+        <v>4285</v>
       </c>
       <c r="B83" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2347,10 +2348,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4320</v>
+        <v>4290</v>
       </c>
       <c r="B84" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C84" t="n">
         <v>0</v>
@@ -2358,54 +2359,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4325</v>
+        <v>4295</v>
       </c>
       <c r="B85" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C85" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4330</v>
+        <v>4300</v>
       </c>
       <c r="B86" t="n">
-        <v>15</v>
+        <v>164</v>
       </c>
       <c r="C86" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4335</v>
+        <v>4305</v>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C87" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4340</v>
+        <v>4310</v>
       </c>
       <c r="B88" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4345</v>
+        <v>4315</v>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
@@ -2413,76 +2414,76 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4350</v>
+        <v>4320</v>
       </c>
       <c r="B90" t="n">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="C90" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4360</v>
+        <v>4325</v>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4370</v>
+        <v>4330</v>
       </c>
       <c r="B92" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C92" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4375</v>
+        <v>4335</v>
       </c>
       <c r="B93" t="n">
-        <v>289</v>
+        <v>2</v>
       </c>
       <c r="C93" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4380</v>
+        <v>4340</v>
       </c>
       <c r="B94" t="n">
+        <v>2</v>
+      </c>
+      <c r="C94" t="n">
         <v>1</v>
-      </c>
-      <c r="C94" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4385</v>
+        <v>4350</v>
       </c>
       <c r="B95" t="n">
-        <v>26</v>
+        <v>373</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4390</v>
+        <v>4355</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96" t="n">
         <v>0</v>
@@ -2490,10 +2491,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4395</v>
+        <v>4360</v>
       </c>
       <c r="B97" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -2501,21 +2502,21 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4400</v>
+        <v>4365</v>
       </c>
       <c r="B98" t="n">
-        <v>119</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4405</v>
+        <v>4370</v>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -2523,21 +2524,21 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4410</v>
+        <v>4375</v>
       </c>
       <c r="B100" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4420</v>
+        <v>4380</v>
       </c>
       <c r="B101" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C101" t="n">
         <v>0</v>
@@ -2545,43 +2546,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4425</v>
+        <v>4390</v>
       </c>
       <c r="B102" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="C102" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4435</v>
+        <v>4400</v>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>378</v>
       </c>
       <c r="C103" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4450</v>
+        <v>4415</v>
       </c>
       <c r="B104" t="n">
-        <v>158</v>
+        <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4455</v>
+        <v>4420</v>
       </c>
       <c r="B105" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C105" t="n">
         <v>0</v>
@@ -2589,43 +2590,43 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4460</v>
+        <v>4425</v>
       </c>
       <c r="B106" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C106" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4475</v>
+        <v>4430</v>
       </c>
       <c r="B107" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4500</v>
+        <v>4435</v>
       </c>
       <c r="B108" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="C108" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4505</v>
+        <v>4440</v>
       </c>
       <c r="B109" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -2633,10 +2634,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4525</v>
+        <v>4445</v>
       </c>
       <c r="B110" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="C110" t="n">
         <v>0</v>
@@ -2644,21 +2645,21 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>4550</v>
+        <v>4450</v>
       </c>
       <c r="B111" t="n">
-        <v>22</v>
+        <v>100</v>
       </c>
       <c r="C111" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4560</v>
+        <v>4455</v>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -2666,10 +2667,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4575</v>
+        <v>4460</v>
       </c>
       <c r="B113" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -2677,10 +2678,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4600</v>
+        <v>4475</v>
       </c>
       <c r="B114" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C114" t="n">
         <v>0</v>
@@ -2688,10 +2689,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4625</v>
+        <v>4480</v>
       </c>
       <c r="B115" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -2699,10 +2700,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4650</v>
+        <v>4485</v>
       </c>
       <c r="B116" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2710,21 +2711,21 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4675</v>
+        <v>4500</v>
       </c>
       <c r="B117" t="n">
-        <v>14</v>
+        <v>237</v>
       </c>
       <c r="C117" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4700</v>
+        <v>4520</v>
       </c>
       <c r="B118" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
@@ -2732,32 +2733,32 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4725</v>
+        <v>4525</v>
       </c>
       <c r="B119" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C119" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4750</v>
+        <v>4550</v>
       </c>
       <c r="B120" t="n">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4775</v>
+        <v>4575</v>
       </c>
       <c r="B121" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -2765,21 +2766,21 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4800</v>
+        <v>4600</v>
       </c>
       <c r="B122" t="n">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="C122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4825</v>
+        <v>4625</v>
       </c>
       <c r="B123" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -2787,10 +2788,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4850</v>
+        <v>4650</v>
       </c>
       <c r="B124" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -2798,10 +2799,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>4900</v>
+        <v>4675</v>
       </c>
       <c r="B125" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -2809,10 +2810,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4925</v>
+        <v>4700</v>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>57</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2820,10 +2821,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4950</v>
+        <v>4725</v>
       </c>
       <c r="B127" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -2831,10 +2832,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4975</v>
+        <v>4750</v>
       </c>
       <c r="B128" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -2842,21 +2843,21 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>5000</v>
+        <v>4775</v>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="C129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>5025</v>
+        <v>4800</v>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -2864,10 +2865,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>5050</v>
+        <v>4825</v>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -2875,10 +2876,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>5100</v>
+        <v>4850</v>
       </c>
       <c r="B132" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -2886,10 +2887,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>5125</v>
+        <v>4900</v>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -2897,10 +2898,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>5200</v>
+        <v>4925</v>
       </c>
       <c r="B134" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
@@ -2908,10 +2909,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>5250</v>
+        <v>4950</v>
       </c>
       <c r="B135" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C135" t="n">
         <v>0</v>
@@ -2919,10 +2920,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>5300</v>
+        <v>4975</v>
       </c>
       <c r="B136" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
@@ -2930,22 +2931,92 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B137" t="n">
+        <v>12</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>5100</v>
+      </c>
+      <c r="B138" t="n">
+        <v>13</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>5200</v>
+      </c>
+      <c r="B139" t="n">
+        <v>2</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>5250</v>
+      </c>
+      <c r="B140" t="n">
+        <v>7</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>5300</v>
+      </c>
+      <c r="B141" t="n">
+        <v>11</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
         <v>5400</v>
       </c>
-      <c r="B137" t="n">
-        <v>3</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138"/>
-    <row r="139"/>
-    <row r="140"/>
-    <row r="141"/>
-    <row r="142"/>
-    <row r="143"/>
-    <row r="144"/>
+      <c r="B142" t="n">
+        <v>11</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>5500</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>5750</v>
+      </c>
+      <c r="B144" t="n">
+        <v>40</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="145"/>
     <row r="146"/>
     <row r="147"/>
@@ -3127,7 +3198,7 @@
         </is>
       </c>
       <c r="F4" s="13" t="n">
-        <v>4186.7</v>
+        <v>4162.3</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="61">
@@ -6223,7 +6294,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" bestFit="1" customWidth="1" style="61" min="1" max="1"/>
@@ -6455,43 +6526,219 @@
     </row>
     <row r="6">
       <c r="A6" s="71" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BB1 Week 1 - OCT 2026 (V26)</t>
+          <t>AB1 Week 5 - SEP 2026 (U26)</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="30" t="n">
-        <v>4186.7</v>
+        <v>4136.4</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>4230</v>
+        <v>4200</v>
       </c>
       <c r="F6" s="31" t="n">
-        <v>0.01034227434494953</v>
+        <v>0.01537568900493191</v>
       </c>
       <c r="G6" s="29" t="n">
         <v>4</v>
       </c>
       <c r="H6" s="32" t="n">
-        <v>1.115485564304462</v>
+        <v>0.8211080160940886</v>
       </c>
       <c r="I6" s="33" t="n">
         <v>1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K6" s="73" t="n">
+        <v>46298.65218100695</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>OCT 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WD1 Week 5 - SEP 2026 (U26)</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>4147.7</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>4235</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>0.02104780962943322</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="32" t="n">
+        <v>0.8326506729081334</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K7" s="73" t="n">
+        <v>46298.65205094907</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>OCT 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="71" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>BB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>4186.7</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>4230</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>0.01034227434494953</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>1.115485564304462</v>
+      </c>
+      <c r="I8" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>PRELIMINARY</t>
         </is>
       </c>
-      <c r="K6" s="73" t="n">
+      <c r="K8" s="73" t="n">
         <v>46296.85222474537</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="71" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E21 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>4202.3</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>4250</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>0.01135092687337882</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" s="32" t="n">
+        <v>1.04210042865891</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K9" s="73" t="n">
+        <v>46298.6519262037</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="71" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MW1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>4215</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>0.01266126900992235</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>0.7856942496493688</v>
+      </c>
+      <c r="I10" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>PRELIMINARY</t>
+        </is>
+      </c>
+      <c r="K10" s="73" t="n">
+        <v>46298.64827216436</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>
@@ -6534,7 +6781,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" s="61">
       <c r="A2" s="36" t="n">
-        <v>4070</v>
+        <v>4020</v>
       </c>
       <c r="B2" s="36" t="n">
         <v>0</v>
@@ -6545,7 +6792,7 @@
     </row>
     <row r="3" ht="15" customHeight="1" s="61">
       <c r="A3" s="36" t="n">
-        <v>4075</v>
+        <v>4025</v>
       </c>
       <c r="B3" s="36" t="n">
         <v>0</v>
@@ -6556,7 +6803,7 @@
     </row>
     <row r="4" ht="15" customHeight="1" s="61">
       <c r="A4" s="36" t="n">
-        <v>4080</v>
+        <v>4030</v>
       </c>
       <c r="B4" s="36" t="n">
         <v>0</v>
@@ -6567,7 +6814,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" s="61">
       <c r="A5" s="36" t="n">
-        <v>4085</v>
+        <v>4035</v>
       </c>
       <c r="B5" s="36" t="n">
         <v>0</v>
@@ -6578,109 +6825,109 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="61">
       <c r="A6" s="36" t="n">
-        <v>4090</v>
+        <v>4040</v>
       </c>
       <c r="B6" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="36" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1" s="61">
       <c r="A7" s="36" t="n">
-        <v>4095</v>
+        <v>4045</v>
       </c>
       <c r="B7" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="36" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="61">
       <c r="A8" s="36" t="n">
-        <v>4100</v>
+        <v>4050</v>
       </c>
       <c r="B8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="61">
       <c r="A9" s="36" t="n">
-        <v>4105</v>
+        <v>4055</v>
       </c>
       <c r="B9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="61">
       <c r="A10" s="36" t="n">
-        <v>4110</v>
+        <v>4060</v>
       </c>
       <c r="B10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="61">
       <c r="A11" s="36" t="n">
-        <v>4115</v>
+        <v>4065</v>
       </c>
       <c r="B11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="61">
       <c r="A12" s="36" t="n">
-        <v>4120</v>
+        <v>4070</v>
       </c>
       <c r="B12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="61">
       <c r="A13" s="36" t="n">
-        <v>4125</v>
+        <v>4075</v>
       </c>
       <c r="B13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="36" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="61">
       <c r="A14" s="36" t="n">
-        <v>4130</v>
+        <v>4080</v>
       </c>
       <c r="B14" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="36" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="61">
       <c r="A15" s="36" t="n">
-        <v>4135</v>
+        <v>4085</v>
       </c>
       <c r="B15" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C15" s="36" t="n">
         <v>3</v>
@@ -6688,131 +6935,131 @@
     </row>
     <row r="16" ht="15" customHeight="1" s="61">
       <c r="A16" s="36" t="n">
-        <v>4140</v>
+        <v>4090</v>
       </c>
       <c r="B16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="61">
       <c r="A17" s="36" t="n">
-        <v>4145</v>
+        <v>4095</v>
       </c>
       <c r="B17" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C17" s="36" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="61">
       <c r="A18" s="36" t="n">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="B18" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="36" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="61">
       <c r="A19" s="36" t="n">
-        <v>4155</v>
+        <v>4105</v>
       </c>
       <c r="B19" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C19" s="36" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="61">
       <c r="A20" s="36" t="n">
-        <v>4160</v>
+        <v>4110</v>
       </c>
       <c r="B20" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="36" t="n">
         <v>1</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="61">
       <c r="A21" s="36" t="n">
-        <v>4165</v>
+        <v>4115</v>
       </c>
       <c r="B21" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21" s="36" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="61">
       <c r="A22" s="36" t="n">
-        <v>4170</v>
+        <v>4120</v>
       </c>
       <c r="B22" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="61">
       <c r="A23" s="36" t="n">
-        <v>4175</v>
+        <v>4125</v>
       </c>
       <c r="B23" s="36" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C23" s="36" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="61">
       <c r="A24" s="36" t="n">
-        <v>4180</v>
+        <v>4130</v>
       </c>
       <c r="B24" s="36" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C24" s="36" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="61">
       <c r="A25" s="36" t="n">
-        <v>4185</v>
+        <v>4135</v>
       </c>
       <c r="B25" s="36" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C25" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="61">
       <c r="A26" s="36" t="n">
-        <v>4190</v>
+        <v>4140</v>
       </c>
       <c r="B26" s="36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C26" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="61">
       <c r="A27" s="36" t="n">
-        <v>4195</v>
+        <v>4145</v>
       </c>
       <c r="B27" s="36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C27" s="36" t="n">
         <v>2</v>
@@ -6820,131 +7067,131 @@
     </row>
     <row r="28" ht="15" customHeight="1" s="61">
       <c r="A28" s="36" t="n">
-        <v>4200</v>
+        <v>4150</v>
       </c>
       <c r="B28" s="36" t="n">
-        <v>71</v>
+        <v>2</v>
       </c>
       <c r="C28" s="36" t="n">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="61">
       <c r="A29" s="36" t="n">
-        <v>4205</v>
+        <v>4155</v>
       </c>
       <c r="B29" s="36" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C29" s="36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="61">
       <c r="A30" s="36" t="n">
-        <v>4210</v>
+        <v>4160</v>
       </c>
       <c r="B30" s="36" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="C30" s="36" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="61">
       <c r="A31" s="36" t="n">
-        <v>4215</v>
+        <v>4165</v>
       </c>
       <c r="B31" s="36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C31" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="61">
       <c r="A32" s="36" t="n">
-        <v>4220</v>
+        <v>4170</v>
       </c>
       <c r="B32" s="36" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C32" s="36" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="61">
       <c r="A33" s="36" t="n">
-        <v>4225</v>
+        <v>4175</v>
       </c>
       <c r="B33" s="36" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C33" s="36" t="n">
-        <v>76</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="61">
       <c r="A34" s="36" t="n">
-        <v>4230</v>
+        <v>4180</v>
       </c>
       <c r="B34" s="36" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="C34" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="61">
       <c r="A35" s="36" t="n">
-        <v>4235</v>
+        <v>4185</v>
       </c>
       <c r="B35" s="36" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C35" s="36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="61">
       <c r="A36" s="36" t="n">
-        <v>4240</v>
+        <v>4190</v>
       </c>
       <c r="B36" s="36" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C36" s="36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="61">
       <c r="A37" s="36" t="n">
-        <v>4245</v>
+        <v>4195</v>
       </c>
       <c r="B37" s="36" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C37" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="61">
       <c r="A38" s="36" t="n">
-        <v>4250</v>
+        <v>4200</v>
       </c>
       <c r="B38" s="36" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C38" s="36" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="61">
       <c r="A39" s="36" t="n">
-        <v>4255</v>
+        <v>4205</v>
       </c>
       <c r="B39" s="36" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C39" s="36" t="n">
         <v>0</v>
@@ -6952,87 +7199,87 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="61">
       <c r="A40" s="36" t="n">
-        <v>4260</v>
+        <v>4210</v>
       </c>
       <c r="B40" s="36" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C40" s="36" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="61">
       <c r="A41" s="36" t="n">
-        <v>4265</v>
+        <v>4215</v>
       </c>
       <c r="B41" s="36" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="C41" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="61">
       <c r="A42" s="36" t="n">
-        <v>4270</v>
+        <v>4220</v>
       </c>
       <c r="B42" s="36" t="n">
+        <v>29</v>
+      </c>
+      <c r="C42" s="36" t="n">
         <v>4</v>
-      </c>
-      <c r="C42" s="36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="61">
       <c r="A43" s="36" t="n">
-        <v>4275</v>
+        <v>4225</v>
       </c>
       <c r="B43" s="36" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C43" s="36" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="61">
       <c r="A44" s="36" t="n">
-        <v>4280</v>
+        <v>4230</v>
       </c>
       <c r="B44" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" s="36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="61">
       <c r="A45" s="36" t="n">
-        <v>4285</v>
+        <v>4235</v>
       </c>
       <c r="B45" s="36" t="n">
+        <v>16</v>
+      </c>
+      <c r="C45" s="36" t="n">
         <v>3</v>
-      </c>
-      <c r="C45" s="36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="61">
       <c r="A46" s="36" t="n">
-        <v>4290</v>
+        <v>4240</v>
       </c>
       <c r="B46" s="36" t="n">
+        <v>7</v>
+      </c>
+      <c r="C46" s="36" t="n">
         <v>1</v>
-      </c>
-      <c r="C46" s="36" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="61">
       <c r="A47" s="36" t="n">
-        <v>4295</v>
+        <v>4245</v>
       </c>
       <c r="B47" s="36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C47" s="36" t="n">
         <v>0</v>
@@ -7040,21 +7287,21 @@
     </row>
     <row r="48" ht="15" customHeight="1" s="61">
       <c r="A48" s="36" t="n">
-        <v>4300</v>
+        <v>4250</v>
       </c>
       <c r="B48" s="36" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C48" s="36" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="61">
       <c r="A49" s="36" t="n">
-        <v>4305</v>
+        <v>4255</v>
       </c>
       <c r="B49" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49" s="36" t="n">
         <v>0</v>
@@ -7062,18 +7309,18 @@
     </row>
     <row r="50" ht="15" customHeight="1" s="61">
       <c r="A50" s="36" t="n">
-        <v>4310</v>
+        <v>4260</v>
       </c>
       <c r="B50" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C50" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="61">
       <c r="A51" s="36" t="n">
-        <v>4315</v>
+        <v>4265</v>
       </c>
       <c r="B51" s="36" t="n">
         <v>0</v>
@@ -7084,10 +7331,10 @@
     </row>
     <row r="52" ht="15" customHeight="1" s="61">
       <c r="A52" s="36" t="n">
-        <v>4320</v>
+        <v>4270</v>
       </c>
       <c r="B52" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52" s="36" t="n">
         <v>0</v>
@@ -7095,21 +7342,21 @@
     </row>
     <row r="53" ht="15" customHeight="1" s="61">
       <c r="A53" s="36" t="n">
-        <v>4325</v>
+        <v>4275</v>
       </c>
       <c r="B53" s="36" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="61">
       <c r="A54" s="36" t="n">
-        <v>4330</v>
+        <v>4280</v>
       </c>
       <c r="B54" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54" s="36" t="n">
         <v>0</v>
@@ -7117,7 +7364,7 @@
     </row>
     <row r="55" ht="15" customHeight="1" s="61">
       <c r="A55" s="36" t="n">
-        <v>4335</v>
+        <v>4285</v>
       </c>
       <c r="B55" s="36" t="n">
         <v>0</v>
@@ -7128,7 +7375,7 @@
     </row>
     <row r="56" ht="15" customHeight="1" s="61">
       <c r="A56" s="36" t="n">
-        <v>4340</v>
+        <v>4290</v>
       </c>
       <c r="B56" s="36" t="n">
         <v>0</v>
@@ -7139,10 +7386,10 @@
     </row>
     <row r="57" ht="15" customHeight="1" s="61">
       <c r="A57" s="36" t="n">
-        <v>4345</v>
+        <v>4295</v>
       </c>
       <c r="B57" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C57" s="36" t="n">
         <v>0</v>
@@ -7150,21 +7397,21 @@
     </row>
     <row r="58" ht="15" customHeight="1" s="61">
       <c r="A58" s="36" t="n">
-        <v>4350</v>
+        <v>4300</v>
       </c>
       <c r="B58" s="36" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C58" s="36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="61">
       <c r="A59" s="36" t="n">
-        <v>4355</v>
+        <v>4305</v>
       </c>
       <c r="B59" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59" s="36" t="n">
         <v>0</v>
@@ -7172,10 +7419,10 @@
     </row>
     <row r="60" ht="15" customHeight="1" s="61">
       <c r="A60" s="36" t="n">
-        <v>4360</v>
+        <v>4310</v>
       </c>
       <c r="B60" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60" s="36" t="n">
         <v>0</v>
@@ -7183,7 +7430,7 @@
     </row>
     <row r="61" ht="15" customHeight="1" s="61">
       <c r="A61" s="36" t="n">
-        <v>4365</v>
+        <v>4315</v>
       </c>
       <c r="B61" s="36" t="n">
         <v>0</v>
@@ -7194,7 +7441,7 @@
     </row>
     <row r="62" ht="15" customHeight="1" s="61">
       <c r="A62" s="36" t="n">
-        <v>4370</v>
+        <v>4320</v>
       </c>
       <c r="B62" s="36" t="n">
         <v>0</v>
@@ -7205,7 +7452,7 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="61">
       <c r="A63" s="36" t="n">
-        <v>4375</v>
+        <v>4325</v>
       </c>
       <c r="B63" s="36" t="n">
         <v>2</v>
@@ -7216,7 +7463,7 @@
     </row>
     <row r="64" ht="15" customHeight="1" s="61">
       <c r="A64" s="36" t="n">
-        <v>4380</v>
+        <v>4330</v>
       </c>
       <c r="B64" s="36" t="n">
         <v>0</v>
@@ -7227,7 +7474,7 @@
     </row>
     <row r="65" ht="15" customHeight="1" s="61">
       <c r="A65" s="36" t="n">
-        <v>4385</v>
+        <v>4335</v>
       </c>
       <c r="B65" s="36" t="n">
         <v>0</v>
@@ -7238,7 +7485,7 @@
     </row>
     <row r="66" ht="15" customHeight="1" s="61">
       <c r="A66" s="36" t="n">
-        <v>4390</v>
+        <v>4340</v>
       </c>
       <c r="B66" s="36" t="n">
         <v>0</v>
@@ -7249,7 +7496,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4395</v>
+        <v>4345</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -7260,18 +7507,18 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4400</v>
+        <v>4350</v>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4405</v>
+        <v>4355</v>
       </c>
       <c r="B69" t="n">
         <v>0</v>
@@ -7282,7 +7529,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4410</v>
+        <v>4360</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -7293,7 +7540,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4415</v>
+        <v>4365</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
@@ -7304,7 +7551,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4420</v>
+        <v>4370</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -7315,7 +7562,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4425</v>
+        <v>4375</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
@@ -7326,7 +7573,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4430</v>
+        <v>4380</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
@@ -7337,7 +7584,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4435</v>
+        <v>4385</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -7348,7 +7595,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4440</v>
+        <v>4390</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
@@ -7359,7 +7606,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4445</v>
+        <v>4395</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -7370,10 +7617,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4450</v>
+        <v>4400</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -7381,35 +7628,235 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
+        <v>4405</v>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>4410</v>
+      </c>
+      <c r="B80" t="n">
+        <v>0</v>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>4415</v>
+      </c>
+      <c r="B81" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>4420</v>
+      </c>
+      <c r="B82" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>4425</v>
+      </c>
+      <c r="B83" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>4430</v>
+      </c>
+      <c r="B84" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>4435</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>4440</v>
+      </c>
+      <c r="B86" t="n">
+        <v>0</v>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>4445</v>
+      </c>
+      <c r="B87" t="n">
+        <v>0</v>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>4450</v>
+      </c>
+      <c r="B88" t="n">
+        <v>0</v>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
         <v>4455</v>
       </c>
-      <c r="B79" t="n">
-        <v>0</v>
-      </c>
-      <c r="C79" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
-    <row r="86"/>
-    <row r="87"/>
-    <row r="88"/>
-    <row r="89"/>
-    <row r="90"/>
-    <row r="91"/>
-    <row r="92"/>
-    <row r="93"/>
-    <row r="94"/>
-    <row r="95"/>
-    <row r="96"/>
-    <row r="97"/>
-    <row r="98"/>
-    <row r="99"/>
+      <c r="B89" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>4460</v>
+      </c>
+      <c r="B90" t="n">
+        <v>0</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>4465</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>4470</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>4475</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>4480</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4485</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>4490</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>4495</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>4505</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="100"/>
     <row r="101"/>
     <row r="102"/>
@@ -7735,7 +8182,7 @@
         </is>
       </c>
       <c r="J6" s="45" t="n">
-        <v>4186.7</v>
+        <v>4162.3</v>
       </c>
       <c r="AB6">
         <f>IF(NOT(ISNUMBER('Gamma Data'!A6)),"",IF((ABS('Gamma Data'!B6)+ABS('Gamma Data'!C6))=0,"",IF(OR(ABS('Gamma Data'!A6-$J$6)&gt;$J$6*$J$26,ABS('Gamma Data'!A6-$J$6)&lt;$J$28),"",(ABS('Gamma Data'!B6)+ABS('Gamma Data'!C6))/MAX(ABS('Gamma Data'!A6-$J$6)/($J$6*0.005),1)+ROW()/1000000000)))</f>
@@ -17651,7 +18098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" bestFit="1" customWidth="1" style="61" min="1" max="1"/>
@@ -17880,6 +18327,52 @@
       </c>
       <c r="N5" s="32" t="n">
         <v>0.4087403598971722</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="71" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G1MV6</t>
+        </is>
+      </c>
+      <c r="C6" s="30" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="D6" s="29" t="n">
+        <v>280</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>339</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Negative GEX (วิ่ง)</t>
+        </is>
+      </c>
+      <c r="H6" s="29" t="n"/>
+      <c r="I6" s="29" t="n">
+        <v>4170</v>
+      </c>
+      <c r="J6" s="73" t="n">
+        <v>46298.64884631945</v>
+      </c>
+      <c r="K6" s="29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="L6" s="29" t="n">
+        <v>4150</v>
+      </c>
+      <c r="M6" s="29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="N6" s="32" t="n">
+        <v>0.170028818443804</v>
       </c>
     </row>
   </sheetData>
@@ -17893,7 +18386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18283,7 +18776,7 @@
         </is>
       </c>
       <c r="Q6" s="73" t="n">
-        <v>46298.43735601926</v>
+        <v>46298.43735601852</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -18293,7 +18786,7 @@
       <c r="S6" s="30" t="n">
         <v>4190.1</v>
       </c>
-      <c r="T6" s="74" t="n">
+      <c r="T6" s="75" t="n">
         <v>7</v>
       </c>
       <c r="U6" t="inlineStr">
@@ -18313,6 +18806,210 @@
       <c r="Y6" s="29" t="n">
         <v>4225</v>
       </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>AB1 Week 5 - SEP 2026 (U26)</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="n">
+        <v>46294</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>4136.4</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F7" s="29" t="n"/>
+      <c r="G7" s="29" t="n"/>
+      <c r="H7" s="30" t="n">
+        <v>4147.7</v>
+      </c>
+      <c r="I7" s="30" t="n">
+        <v>4185.4</v>
+      </c>
+      <c r="J7" s="30" t="n">
+        <v>4116.3</v>
+      </c>
+      <c r="K7" s="30" t="n">
+        <v>63.60000000000036</v>
+      </c>
+      <c r="L7" s="30" t="n">
+        <v>52.30000000000018</v>
+      </c>
+      <c r="M7" s="30" t="n">
+        <v>11.30000000000018</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7" s="31" t="n">
+        <v>0.0167053476452953</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q7" s="73" t="n">
+        <v>46298.65528628538</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>OCT 26</t>
+        </is>
+      </c>
+      <c r="S7" s="30" t="n">
+        <v>4117.6</v>
+      </c>
+      <c r="T7" s="75" t="n">
+        <v>-151.4</v>
+      </c>
+      <c r="V7" s="32" t="n"/>
+      <c r="W7" s="29" t="n"/>
+      <c r="X7" s="29" t="n"/>
+      <c r="Y7" s="29" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="71" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WD1 Week 5 - SEP 2026 (U26)</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="n">
+        <v>46295</v>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>4147.7</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>4235</v>
+      </c>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="30" t="n">
+        <v>4155.6</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <v>4217.4</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>4151.4</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>87.30000000000018</v>
+      </c>
+      <c r="L8" s="30" t="n">
+        <v>79.39999999999964</v>
+      </c>
+      <c r="M8" s="30" t="n">
+        <v>7.900000000000546</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8" s="31" t="n">
+        <v>0.01591243339682234</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q8" s="73" t="n">
+        <v>46298.65528985655</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>OCT 26</t>
+        </is>
+      </c>
+      <c r="S8" s="30" t="n">
+        <v>4183.8</v>
+      </c>
+      <c r="T8" s="75" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="V8" s="32" t="n"/>
+      <c r="W8" s="29" t="n"/>
+      <c r="X8" s="29" t="n"/>
+      <c r="Y8" s="29" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="71" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>E21 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="n">
+        <v>46297</v>
+      </c>
+      <c r="D9" s="30" t="n">
+        <v>4202.3</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>4250</v>
+      </c>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="30" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="I9" s="30" t="n">
+        <v>4259</v>
+      </c>
+      <c r="J9" s="30" t="n">
+        <v>4153.8</v>
+      </c>
+      <c r="K9" s="30" t="n">
+        <v>47.69999999999982</v>
+      </c>
+      <c r="L9" s="30" t="n">
+        <v>87.69999999999982</v>
+      </c>
+      <c r="M9" s="30" t="n">
+        <v>40</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9" s="31" t="n">
+        <v>0.02503391000166571</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q9" s="73" t="n">
+        <v>46298.65529687911</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+      <c r="S9" s="30" t="n">
+        <v>4204.6</v>
+      </c>
+      <c r="T9" s="75" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="V9" s="32" t="n"/>
+      <c r="W9" s="29" t="n"/>
+      <c r="X9" s="29" t="n"/>
+      <c r="Y9" s="29" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/MaxPain_GEX.xlsx
+++ b/MaxPain_GEX.xlsx
@@ -14,6 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="บันทึกโหมด" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GEX Log" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Outcome" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Log รวม" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -22,7 +23,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="15">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="\+#,##0.0;\-#,##0.0"/>
     <numFmt numFmtId="166" formatCode="\+0.0%;\-0.0%"/>
@@ -37,7 +38,8 @@
     <numFmt numFmtId="175" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="176" formatCode="yyyy-mm-dd hh:mm"/>
     <numFmt numFmtId="177" formatCode="+0.0;-0.0"/>
-    <numFmt numFmtId="178" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="178" formatCode="0.000"/>
+    <numFmt numFmtId="179" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -383,7 +385,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -552,6 +554,8 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -954,12 +958,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Max Pain Calc'!$A$2:$A$144</f>
+              <f>'Max Pain Calc'!$A$2:$A$134</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Max Pain Calc'!$B$2:$B$144</f>
+              <f>'Max Pain Calc'!$B$2:$B$134</f>
             </numRef>
           </val>
         </ser>
@@ -1032,12 +1036,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'GEX Calc'!$A$2:$A$99</f>
+              <f>'GEX Calc'!$A$2:$A$104</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'GEX Calc'!$C$2:$C$99</f>
+              <f>'GEX Calc'!$C$2:$C$104</f>
             </numRef>
           </val>
         </ser>
@@ -1379,13 +1383,13 @@
     </row>
     <row r="2" ht="25.5" customHeight="1" s="61">
       <c r="A2" s="2" t="n">
-        <v>3600</v>
+        <v>3000</v>
       </c>
       <c r="B2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
@@ -1394,7 +1398,7 @@
       </c>
       <c r="F2" s="26" t="inlineStr">
         <is>
-          <t>MW1 Week 1 - OCT 2026 (V26)</t>
+          <t>E21 Week 2 - OCT 2026 (V26)</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1405,13 +1409,13 @@
     </row>
     <row r="3" ht="25.5" customHeight="1" s="61">
       <c r="A3" s="2" t="n">
-        <v>3700</v>
+        <v>3250</v>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
@@ -1419,7 +1423,7 @@
         </is>
       </c>
       <c r="F3" s="27" t="n">
-        <v>46297</v>
+        <v>46302</v>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
@@ -1429,13 +1433,13 @@
     </row>
     <row r="4" ht="25.5" customHeight="1" s="61">
       <c r="A4" s="2" t="n">
-        <v>3750</v>
+        <v>3500</v>
       </c>
       <c r="B4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
@@ -1443,7 +1447,7 @@
         </is>
       </c>
       <c r="F4" s="26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
@@ -1453,13 +1457,13 @@
     </row>
     <row r="5" ht="25.5" customHeight="1" s="61">
       <c r="A5" s="2" t="n">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1467,7 +1471,7 @@
         </is>
       </c>
       <c r="F5" s="26" t="n">
-        <v>3565</v>
+        <v>6721</v>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
@@ -1477,13 +1481,13 @@
     </row>
     <row r="6" ht="25.5" customHeight="1" s="61">
       <c r="A6" s="2" t="n">
-        <v>3805</v>
+        <v>3700</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
@@ -1491,7 +1495,7 @@
         </is>
       </c>
       <c r="F6" s="26" t="n">
-        <v>2801</v>
+        <v>5835</v>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
@@ -1501,725 +1505,725 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="61">
       <c r="A7" s="2" t="n">
-        <v>3820</v>
+        <v>3750</v>
       </c>
       <c r="B7" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>13</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="15" customHeight="1" s="61">
       <c r="A8" s="2" t="n">
-        <v>3825</v>
+        <v>3775</v>
       </c>
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="61">
       <c r="A9" s="2" t="n">
-        <v>3880</v>
+        <v>3780</v>
       </c>
       <c r="B9" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="61">
       <c r="A10" s="2" t="n">
-        <v>3895</v>
+        <v>3795</v>
       </c>
       <c r="B10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="61">
       <c r="A11" s="2" t="n">
-        <v>3900</v>
+        <v>3800</v>
       </c>
       <c r="B11" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>33</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="61">
       <c r="A12" s="2" t="n">
-        <v>3905</v>
+        <v>3810</v>
       </c>
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="61">
       <c r="A13" s="2" t="n">
-        <v>3915</v>
+        <v>3825</v>
       </c>
       <c r="B13" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="61">
       <c r="A14" s="2" t="n">
-        <v>3925</v>
+        <v>3830</v>
       </c>
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="61">
       <c r="A15" s="2" t="n">
-        <v>3935</v>
+        <v>3850</v>
       </c>
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="61">
       <c r="A16" s="2" t="n">
-        <v>3940</v>
+        <v>3855</v>
       </c>
       <c r="B16" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="61">
       <c r="A17" s="2" t="n">
-        <v>3950</v>
+        <v>3865</v>
       </c>
       <c r="B17" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="61">
       <c r="A18" s="2" t="n">
-        <v>3955</v>
+        <v>3880</v>
       </c>
       <c r="B18" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="61">
       <c r="A19" s="2" t="n">
-        <v>3960</v>
+        <v>3890</v>
       </c>
       <c r="B19" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="61">
       <c r="A20" s="2" t="n">
-        <v>3965</v>
+        <v>3900</v>
       </c>
       <c r="B20" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>3</v>
+        <v>173</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="61">
       <c r="A21" s="2" t="n">
-        <v>3970</v>
+        <v>3915</v>
       </c>
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="61">
       <c r="A22" s="2" t="n">
-        <v>3975</v>
+        <v>3925</v>
       </c>
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="61">
       <c r="A23" s="2" t="n">
-        <v>3980</v>
+        <v>3930</v>
       </c>
       <c r="B23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="61">
       <c r="A24" s="2" t="n">
-        <v>3985</v>
+        <v>3945</v>
       </c>
       <c r="B24" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="61">
       <c r="A25" s="2" t="n">
-        <v>3995</v>
+        <v>3950</v>
       </c>
       <c r="B25" s="3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>6</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" s="61">
       <c r="A26" s="2" t="n">
-        <v>4000</v>
+        <v>3955</v>
       </c>
       <c r="B26" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>57</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="61">
       <c r="A27" s="2" t="n">
-        <v>4005</v>
+        <v>3960</v>
       </c>
       <c r="B27" s="3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="61">
       <c r="A28" s="2" t="n">
-        <v>4010</v>
+        <v>3970</v>
       </c>
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="61">
       <c r="A29" s="2" t="n">
-        <v>4015</v>
+        <v>3975</v>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="61">
       <c r="A30" s="2" t="n">
-        <v>4020</v>
+        <v>3980</v>
       </c>
       <c r="B30" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="61">
       <c r="A31" s="2" t="n">
-        <v>4025</v>
+        <v>3985</v>
       </c>
       <c r="B31" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>101</v>
+        <v>11</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="61">
       <c r="A32" s="2" t="n">
-        <v>4030</v>
+        <v>3990</v>
       </c>
       <c r="B32" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="61">
       <c r="A33" s="2" t="n">
-        <v>4035</v>
+        <v>3995</v>
       </c>
       <c r="B33" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="61">
       <c r="A34" s="2" t="n">
-        <v>4040</v>
+        <v>4000</v>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>9</v>
+        <v>841</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="61">
       <c r="A35" s="2" t="n">
-        <v>4045</v>
+        <v>4005</v>
       </c>
       <c r="B35" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="61">
       <c r="A36" s="2" t="n">
-        <v>4050</v>
+        <v>4010</v>
       </c>
       <c r="B36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>344</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="61">
       <c r="A37" s="2" t="n">
-        <v>4055</v>
+        <v>4015</v>
       </c>
       <c r="B37" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="61">
       <c r="A38" s="2" t="n">
-        <v>4060</v>
+        <v>4020</v>
       </c>
       <c r="B38" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="61">
       <c r="A39" s="2" t="n">
-        <v>4065</v>
+        <v>4025</v>
       </c>
       <c r="B39" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="61">
       <c r="A40" s="2" t="n">
-        <v>4070</v>
+        <v>4030</v>
       </c>
       <c r="B40" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="61">
       <c r="A41" s="2" t="n">
-        <v>4075</v>
+        <v>4035</v>
       </c>
       <c r="B41" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>242</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="61">
       <c r="A42" s="2" t="n">
-        <v>4080</v>
+        <v>4040</v>
       </c>
       <c r="B42" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="3" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="61">
       <c r="A43" s="2" t="n">
-        <v>4085</v>
+        <v>4045</v>
       </c>
       <c r="B43" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="3" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="61">
       <c r="A44" s="2" t="n">
-        <v>4090</v>
+        <v>4050</v>
       </c>
       <c r="B44" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>22</v>
+        <v>781</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="61">
       <c r="A45" s="2" t="n">
-        <v>4095</v>
+        <v>4055</v>
       </c>
       <c r="B45" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="61">
       <c r="A46" s="2" t="n">
-        <v>4100</v>
+        <v>4060</v>
       </c>
       <c r="B46" s="3" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>237</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="61">
       <c r="A47" s="2" t="n">
-        <v>4105</v>
+        <v>4065</v>
       </c>
       <c r="B47" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1" s="61">
       <c r="A48" s="2" t="n">
-        <v>4110</v>
+        <v>4070</v>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="61">
       <c r="A49" s="2" t="n">
-        <v>4115</v>
+        <v>4075</v>
       </c>
       <c r="B49" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1</v>
+        <v>353</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1" s="61">
       <c r="A50" s="2" t="n">
-        <v>4120</v>
+        <v>4080</v>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="61">
       <c r="A51" s="2" t="n">
-        <v>4125</v>
+        <v>4085</v>
       </c>
       <c r="B51" s="3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C51" s="3" t="n">
-        <v>48</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1" s="61">
       <c r="A52" s="2" t="n">
-        <v>4130</v>
+        <v>4090</v>
       </c>
       <c r="B52" s="3" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C52" s="3" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>4135</v>
+        <v>4095</v>
       </c>
       <c r="B53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="61">
       <c r="A54" s="2" t="n">
-        <v>4140</v>
+        <v>4100</v>
       </c>
       <c r="B54" s="3" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="C54" s="3" t="n">
-        <v>12</v>
+        <v>719</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="61">
       <c r="A55" s="2" t="n">
-        <v>4145</v>
+        <v>4105</v>
       </c>
       <c r="B55" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C55" s="3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1" s="61">
       <c r="A56" s="2" t="n">
-        <v>4150</v>
+        <v>4110</v>
       </c>
       <c r="B56" s="3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C56" s="3" t="n">
-        <v>153</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>4155</v>
+        <v>4115</v>
       </c>
       <c r="B57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C57" s="3" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>4160</v>
+        <v>4120</v>
       </c>
       <c r="B58" s="3" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>4165</v>
+        <v>4125</v>
       </c>
       <c r="B59" s="3" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C59" s="3" t="n">
-        <v>15</v>
+        <v>110</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>4170</v>
+        <v>4130</v>
       </c>
       <c r="B60" s="3" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="C60" s="3" t="n">
-        <v>103</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>4175</v>
+        <v>4135</v>
       </c>
       <c r="B61" s="3" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C61" s="3" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>4180</v>
+        <v>4140</v>
       </c>
       <c r="B62" s="3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C62" s="3" t="n">
-        <v>24</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>4185</v>
+        <v>4145</v>
       </c>
       <c r="B63" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>4190</v>
+        <v>4150</v>
       </c>
       <c r="B64" t="n">
-        <v>111</v>
+        <v>57</v>
       </c>
       <c r="C64" t="n">
-        <v>17</v>
+        <v>318</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>4195</v>
+        <v>4155</v>
       </c>
       <c r="B65" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="C65" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>4200</v>
+        <v>4160</v>
       </c>
       <c r="B66" t="n">
-        <v>82</v>
+        <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>54</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4205</v>
+        <v>4165</v>
       </c>
       <c r="B67" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C67" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4210</v>
+        <v>4170</v>
       </c>
       <c r="B68" t="n">
-        <v>81</v>
+        <v>36</v>
       </c>
       <c r="C68" t="n">
-        <v>121</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4215</v>
+        <v>4175</v>
       </c>
       <c r="B69" t="n">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C69" t="n">
-        <v>21</v>
+        <v>214</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4220</v>
+        <v>4180</v>
       </c>
       <c r="B70" t="n">
-        <v>169</v>
+        <v>38</v>
       </c>
       <c r="C70" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4225</v>
+        <v>4185</v>
       </c>
       <c r="B71" t="n">
-        <v>161</v>
+        <v>47</v>
       </c>
       <c r="C71" t="n">
-        <v>81</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4230</v>
+        <v>4190</v>
       </c>
       <c r="B72" t="n">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="C72" t="n">
         <v>26</v>
@@ -2227,54 +2231,54 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4235</v>
+        <v>4195</v>
       </c>
       <c r="B73" t="n">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="C73" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4240</v>
+        <v>4200</v>
       </c>
       <c r="B74" t="n">
-        <v>63</v>
+        <v>581</v>
       </c>
       <c r="C74" t="n">
-        <v>6</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4245</v>
+        <v>4205</v>
       </c>
       <c r="B75" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4250</v>
+        <v>4210</v>
       </c>
       <c r="B76" t="n">
-        <v>104</v>
+        <v>19</v>
       </c>
       <c r="C76" t="n">
-        <v>82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4255</v>
+        <v>4215</v>
       </c>
       <c r="B77" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C77" t="n">
         <v>0</v>
@@ -2282,32 +2286,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4260</v>
+        <v>4220</v>
       </c>
       <c r="B78" t="n">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C78" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4265</v>
+        <v>4225</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>113</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
+        <v>73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4270</v>
+        <v>4230</v>
       </c>
       <c r="B80" t="n">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C80" t="n">
         <v>0</v>
@@ -2315,32 +2319,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4275</v>
+        <v>4235</v>
       </c>
       <c r="B81" t="n">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="C81" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4280</v>
+        <v>4240</v>
       </c>
       <c r="B82" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4285</v>
+        <v>4245</v>
       </c>
       <c r="B83" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2348,43 +2352,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4290</v>
+        <v>4250</v>
       </c>
       <c r="B84" t="n">
-        <v>11</v>
+        <v>343</v>
       </c>
       <c r="C84" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4295</v>
+        <v>4255</v>
       </c>
       <c r="B85" t="n">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C85" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4300</v>
+        <v>4260</v>
       </c>
       <c r="B86" t="n">
-        <v>164</v>
+        <v>22</v>
       </c>
       <c r="C86" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4305</v>
+        <v>4265</v>
       </c>
       <c r="B87" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2392,10 +2396,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4310</v>
+        <v>4270</v>
       </c>
       <c r="B88" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2403,153 +2407,153 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>270</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4320</v>
+        <v>4280</v>
       </c>
       <c r="B90" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4325</v>
+        <v>4285</v>
       </c>
       <c r="B91" t="n">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="C91" t="n">
-        <v>69</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4330</v>
+        <v>4290</v>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C92" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4335</v>
+        <v>4300</v>
       </c>
       <c r="B93" t="n">
-        <v>2</v>
+        <v>581</v>
       </c>
       <c r="C93" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4340</v>
+        <v>4305</v>
       </c>
       <c r="B94" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4350</v>
+        <v>4310</v>
       </c>
       <c r="B95" t="n">
-        <v>373</v>
+        <v>6</v>
       </c>
       <c r="C95" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4355</v>
+        <v>4315</v>
       </c>
       <c r="B96" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4360</v>
+        <v>4320</v>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4365</v>
+        <v>4325</v>
       </c>
       <c r="B98" t="n">
-        <v>2</v>
+        <v>135</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>4370</v>
+        <v>4330</v>
       </c>
       <c r="B99" t="n">
+        <v>21</v>
+      </c>
+      <c r="C99" t="n">
         <v>1</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>4375</v>
+        <v>4340</v>
       </c>
       <c r="B100" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C100" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>4380</v>
+        <v>4350</v>
       </c>
       <c r="B101" t="n">
-        <v>3</v>
+        <v>313</v>
       </c>
       <c r="C101" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>4390</v>
+        <v>4355</v>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C102" t="n">
         <v>0</v>
@@ -2557,21 +2561,21 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>4400</v>
+        <v>4360</v>
       </c>
       <c r="B103" t="n">
-        <v>378</v>
+        <v>5</v>
       </c>
       <c r="C103" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>4415</v>
+        <v>4370</v>
       </c>
       <c r="B104" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="C104" t="n">
         <v>0</v>
@@ -2579,43 +2583,43 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>4420</v>
+        <v>4375</v>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="C105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>4425</v>
+        <v>4380</v>
       </c>
       <c r="B106" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C106" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>4430</v>
+        <v>4400</v>
       </c>
       <c r="B107" t="n">
-        <v>10</v>
+        <v>634</v>
       </c>
       <c r="C107" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>4435</v>
+        <v>4405</v>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
@@ -2623,10 +2627,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>4440</v>
+        <v>4425</v>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>516</v>
       </c>
       <c r="C109" t="n">
         <v>0</v>
@@ -2634,7 +2638,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>4445</v>
+        <v>4440</v>
       </c>
       <c r="B110" t="n">
         <v>1</v>
@@ -2651,15 +2655,15 @@
         <v>100</v>
       </c>
       <c r="C111" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>4455</v>
+        <v>4465</v>
       </c>
       <c r="B112" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
@@ -2667,10 +2671,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>4460</v>
+        <v>4475</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>429</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
@@ -2678,21 +2682,21 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>4475</v>
+        <v>4500</v>
       </c>
       <c r="B114" t="n">
-        <v>20</v>
+        <v>540</v>
       </c>
       <c r="C114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>4480</v>
+        <v>4525</v>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>57</v>
       </c>
       <c r="C115" t="n">
         <v>0</v>
@@ -2700,10 +2704,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>4485</v>
+        <v>4535</v>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C116" t="n">
         <v>0</v>
@@ -2711,54 +2715,54 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>4500</v>
+        <v>4550</v>
       </c>
       <c r="B117" t="n">
-        <v>237</v>
+        <v>72</v>
       </c>
       <c r="C117" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>4520</v>
+        <v>4575</v>
       </c>
       <c r="B118" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="C118" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>4525</v>
+        <v>4600</v>
       </c>
       <c r="B119" t="n">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="C119" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>4550</v>
+        <v>4625</v>
       </c>
       <c r="B120" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4575</v>
+        <v>4650</v>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C121" t="n">
         <v>0</v>
@@ -2766,21 +2770,21 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>4600</v>
+        <v>4675</v>
       </c>
       <c r="B122" t="n">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="C122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>4625</v>
+        <v>4700</v>
       </c>
       <c r="B123" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C123" t="n">
         <v>0</v>
@@ -2788,10 +2792,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>4650</v>
+        <v>4725</v>
       </c>
       <c r="B124" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="C124" t="n">
         <v>0</v>
@@ -2799,10 +2803,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>4675</v>
+        <v>4750</v>
       </c>
       <c r="B125" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="C125" t="n">
         <v>0</v>
@@ -2810,10 +2814,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>4700</v>
+        <v>4775</v>
       </c>
       <c r="B126" t="n">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
@@ -2821,10 +2825,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>4725</v>
+        <v>4800</v>
       </c>
       <c r="B127" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C127" t="n">
         <v>0</v>
@@ -2832,10 +2836,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>4750</v>
+        <v>4850</v>
       </c>
       <c r="B128" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C128" t="n">
         <v>0</v>
@@ -2843,21 +2847,21 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>4775</v>
+        <v>4900</v>
       </c>
       <c r="B129" t="n">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>172</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
@@ -2865,10 +2869,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>4825</v>
+        <v>5100</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>97</v>
       </c>
       <c r="C131" t="n">
         <v>0</v>
@@ -2876,10 +2880,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>4850</v>
+        <v>5200</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C132" t="n">
         <v>0</v>
@@ -2887,10 +2891,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4900</v>
+        <v>5250</v>
       </c>
       <c r="B133" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C133" t="n">
         <v>0</v>
@@ -2898,125 +2902,25 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>4925</v>
+        <v>10000</v>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>4950</v>
-      </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
-      <c r="C135" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>4975</v>
-      </c>
-      <c r="B136" t="n">
-        <v>2</v>
-      </c>
-      <c r="C136" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>5000</v>
-      </c>
-      <c r="B137" t="n">
-        <v>12</v>
-      </c>
-      <c r="C137" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>5100</v>
-      </c>
-      <c r="B138" t="n">
-        <v>13</v>
-      </c>
-      <c r="C138" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>5200</v>
-      </c>
-      <c r="B139" t="n">
-        <v>2</v>
-      </c>
-      <c r="C139" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>5250</v>
-      </c>
-      <c r="B140" t="n">
-        <v>7</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>5300</v>
-      </c>
-      <c r="B141" t="n">
-        <v>11</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>5400</v>
-      </c>
-      <c r="B142" t="n">
-        <v>11</v>
-      </c>
-      <c r="C142" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>5500</v>
-      </c>
-      <c r="B143" t="n">
-        <v>8</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>5750</v>
-      </c>
-      <c r="B144" t="n">
-        <v>40</v>
-      </c>
-      <c r="C144" t="n">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="135"/>
+    <row r="136"/>
+    <row r="137"/>
+    <row r="138"/>
+    <row r="139"/>
+    <row r="140"/>
+    <row r="141"/>
+    <row r="142"/>
+    <row r="143"/>
+    <row r="144"/>
     <row r="145"/>
     <row r="146"/>
     <row r="147"/>
@@ -3198,7 +3102,7 @@
         </is>
       </c>
       <c r="F4" s="13" t="n">
-        <v>4162.3</v>
+        <v>4140.7</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="61">
@@ -6294,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" bestFit="1" customWidth="1" style="61" min="1" max="1"/>
@@ -6739,6 +6643,138 @@
         <v>46298.64827216436</v>
       </c>
       <c r="L10" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="71" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>4156.8</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>4185</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>0.006784064665126976</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="32" t="n">
+        <v>0.921875</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K11" s="73" t="n">
+        <v>46304.5094819213</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WD1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>4187.1</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>0.003080891309020476</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="32" t="n">
+        <v>0.6609140300415468</v>
+      </c>
+      <c r="I12" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K12" s="73" t="n">
+        <v>46304.50934444444</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="71" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>E21 Week 2 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="30" t="n">
+        <v>4140.7</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>0.01190619943487821</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="32" t="n">
+        <v>0.8681743788126767</v>
+      </c>
+      <c r="I13" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>FINAL</t>
+        </is>
+      </c>
+      <c r="K13" s="73" t="n">
+        <v>46304.50813082176</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>DEC 26</t>
         </is>
@@ -6781,7 +6817,7 @@
     </row>
     <row r="2" ht="15" customHeight="1" s="61">
       <c r="A2" s="36" t="n">
-        <v>4020</v>
+        <v>3995</v>
       </c>
       <c r="B2" s="36" t="n">
         <v>0</v>
@@ -6792,29 +6828,29 @@
     </row>
     <row r="3" ht="15" customHeight="1" s="61">
       <c r="A3" s="36" t="n">
-        <v>4025</v>
+        <v>4000</v>
       </c>
       <c r="B3" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="36" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" ht="15" customHeight="1" s="61">
       <c r="A4" s="36" t="n">
-        <v>4030</v>
+        <v>4005</v>
       </c>
       <c r="B4" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C4" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" ht="15" customHeight="1" s="61">
       <c r="A5" s="36" t="n">
-        <v>4035</v>
+        <v>4010</v>
       </c>
       <c r="B5" s="36" t="n">
         <v>0</v>
@@ -6825,7 +6861,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" s="61">
       <c r="A6" s="36" t="n">
-        <v>4040</v>
+        <v>4015</v>
       </c>
       <c r="B6" s="36" t="n">
         <v>0</v>
@@ -6836,7 +6872,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="61">
       <c r="A7" s="36" t="n">
-        <v>4045</v>
+        <v>4020</v>
       </c>
       <c r="B7" s="36" t="n">
         <v>0</v>
@@ -6847,73 +6883,73 @@
     </row>
     <row r="8" ht="15" customHeight="1" s="61">
       <c r="A8" s="36" t="n">
-        <v>4050</v>
+        <v>4025</v>
       </c>
       <c r="B8" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="36" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="61">
       <c r="A9" s="36" t="n">
-        <v>4055</v>
+        <v>4030</v>
       </c>
       <c r="B9" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="61">
       <c r="A10" s="36" t="n">
-        <v>4060</v>
+        <v>4035</v>
       </c>
       <c r="B10" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C10" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="15" customHeight="1" s="61">
       <c r="A11" s="36" t="n">
-        <v>4065</v>
+        <v>4040</v>
       </c>
       <c r="B11" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C11" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="61">
       <c r="A12" s="36" t="n">
-        <v>4070</v>
+        <v>4045</v>
       </c>
       <c r="B12" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C12" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="61">
       <c r="A13" s="36" t="n">
-        <v>4075</v>
+        <v>4050</v>
       </c>
       <c r="B13" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C13" s="36" t="n">
-        <v>21</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1" s="61">
       <c r="A14" s="36" t="n">
-        <v>4080</v>
+        <v>4055</v>
       </c>
       <c r="B14" s="36" t="n">
         <v>0</v>
@@ -6924,117 +6960,117 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="61">
       <c r="A15" s="36" t="n">
-        <v>4085</v>
+        <v>4060</v>
       </c>
       <c r="B15" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C15" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="61">
       <c r="A16" s="36" t="n">
-        <v>4090</v>
+        <v>4065</v>
       </c>
       <c r="B16" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C16" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1" s="61">
       <c r="A17" s="36" t="n">
-        <v>4095</v>
+        <v>4070</v>
       </c>
       <c r="B17" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1" s="61">
       <c r="A18" s="36" t="n">
-        <v>4100</v>
+        <v>4075</v>
       </c>
       <c r="B18" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="36" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="19" ht="15" customHeight="1" s="61">
       <c r="A19" s="36" t="n">
-        <v>4105</v>
+        <v>4080</v>
       </c>
       <c r="B19" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C19" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="61">
       <c r="A20" s="36" t="n">
-        <v>4110</v>
+        <v>4085</v>
       </c>
       <c r="B20" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C20" s="36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1" s="61">
       <c r="A21" s="36" t="n">
-        <v>4115</v>
+        <v>4090</v>
       </c>
       <c r="B21" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C21" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" ht="15" customHeight="1" s="61">
       <c r="A22" s="36" t="n">
-        <v>4120</v>
+        <v>4095</v>
       </c>
       <c r="B22" s="36" t="n">
         <v>0</v>
       </c>
       <c r="C22" s="36" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="61">
       <c r="A23" s="36" t="n">
-        <v>4125</v>
+        <v>4100</v>
       </c>
       <c r="B23" s="36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C23" s="36" t="n">
-        <v>11</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="61">
       <c r="A24" s="36" t="n">
-        <v>4130</v>
+        <v>4105</v>
       </c>
       <c r="B24" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" s="36" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1" s="61">
       <c r="A25" s="36" t="n">
-        <v>4135</v>
+        <v>4110</v>
       </c>
       <c r="B25" s="36" t="n">
         <v>0</v>
@@ -7045,241 +7081,241 @@
     </row>
     <row r="26" ht="15" customHeight="1" s="61">
       <c r="A26" s="36" t="n">
-        <v>4140</v>
+        <v>4115</v>
       </c>
       <c r="B26" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C26" s="36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" s="61">
       <c r="A27" s="36" t="n">
-        <v>4145</v>
+        <v>4120</v>
       </c>
       <c r="B27" s="36" t="n">
         <v>1</v>
       </c>
       <c r="C27" s="36" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1" s="61">
       <c r="A28" s="36" t="n">
-        <v>4150</v>
+        <v>4125</v>
       </c>
       <c r="B28" s="36" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C28" s="36" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1" s="61">
       <c r="A29" s="36" t="n">
-        <v>4155</v>
+        <v>4130</v>
       </c>
       <c r="B29" s="36" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C29" s="36" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30" ht="15" customHeight="1" s="61">
       <c r="A30" s="36" t="n">
-        <v>4160</v>
+        <v>4135</v>
       </c>
       <c r="B30" s="36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C30" s="36" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="61">
       <c r="A31" s="36" t="n">
-        <v>4165</v>
+        <v>4140</v>
       </c>
       <c r="B31" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" s="36" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="61">
       <c r="A32" s="36" t="n">
-        <v>4170</v>
+        <v>4145</v>
       </c>
       <c r="B32" s="36" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C32" s="36" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1" s="61">
       <c r="A33" s="36" t="n">
-        <v>4175</v>
+        <v>4150</v>
       </c>
       <c r="B33" s="36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C33" s="36" t="n">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="61">
       <c r="A34" s="36" t="n">
-        <v>4180</v>
+        <v>4155</v>
       </c>
       <c r="B34" s="36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C34" s="36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="61">
       <c r="A35" s="36" t="n">
-        <v>4185</v>
+        <v>4160</v>
       </c>
       <c r="B35" s="36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" s="36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1" s="61">
       <c r="A36" s="36" t="n">
-        <v>4190</v>
+        <v>4165</v>
       </c>
       <c r="B36" s="36" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="C36" s="36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1" s="61">
       <c r="A37" s="36" t="n">
-        <v>4195</v>
+        <v>4170</v>
       </c>
       <c r="B37" s="36" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C37" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="61">
       <c r="A38" s="36" t="n">
-        <v>4200</v>
+        <v>4175</v>
       </c>
       <c r="B38" s="36" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C38" s="36" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="61">
       <c r="A39" s="36" t="n">
-        <v>4205</v>
+        <v>4180</v>
       </c>
       <c r="B39" s="36" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C39" s="36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="61">
       <c r="A40" s="36" t="n">
-        <v>4210</v>
+        <v>4185</v>
       </c>
       <c r="B40" s="36" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C40" s="36" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1" s="61">
       <c r="A41" s="36" t="n">
-        <v>4215</v>
+        <v>4190</v>
       </c>
       <c r="B41" s="36" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="C41" s="36" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="61">
       <c r="A42" s="36" t="n">
-        <v>4220</v>
+        <v>4195</v>
       </c>
       <c r="B42" s="36" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C42" s="36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="61">
       <c r="A43" s="36" t="n">
-        <v>4225</v>
+        <v>4200</v>
       </c>
       <c r="B43" s="36" t="n">
-        <v>25</v>
+        <v>98</v>
       </c>
       <c r="C43" s="36" t="n">
-        <v>13</v>
+        <v>47</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="61">
       <c r="A44" s="36" t="n">
-        <v>4230</v>
+        <v>4205</v>
       </c>
       <c r="B44" s="36" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C44" s="36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1" s="61">
       <c r="A45" s="36" t="n">
-        <v>4235</v>
+        <v>4210</v>
       </c>
       <c r="B45" s="36" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="C45" s="36" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1" s="61">
       <c r="A46" s="36" t="n">
-        <v>4240</v>
+        <v>4215</v>
       </c>
       <c r="B46" s="36" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C46" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1" s="61">
       <c r="A47" s="36" t="n">
-        <v>4245</v>
+        <v>4220</v>
       </c>
       <c r="B47" s="36" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C47" s="36" t="n">
         <v>0</v>
@@ -7287,21 +7323,21 @@
     </row>
     <row r="48" ht="15" customHeight="1" s="61">
       <c r="A48" s="36" t="n">
-        <v>4250</v>
+        <v>4225</v>
       </c>
       <c r="B48" s="36" t="n">
+        <v>14</v>
+      </c>
+      <c r="C48" s="36" t="n">
         <v>9</v>
-      </c>
-      <c r="C48" s="36" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="61">
       <c r="A49" s="36" t="n">
-        <v>4255</v>
+        <v>4230</v>
       </c>
       <c r="B49" s="36" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C49" s="36" t="n">
         <v>0</v>
@@ -7309,21 +7345,21 @@
     </row>
     <row r="50" ht="15" customHeight="1" s="61">
       <c r="A50" s="36" t="n">
-        <v>4260</v>
+        <v>4235</v>
       </c>
       <c r="B50" s="36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50" s="36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" s="61">
       <c r="A51" s="36" t="n">
-        <v>4265</v>
+        <v>4240</v>
       </c>
       <c r="B51" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51" s="36" t="n">
         <v>0</v>
@@ -7331,10 +7367,10 @@
     </row>
     <row r="52" ht="15" customHeight="1" s="61">
       <c r="A52" s="36" t="n">
-        <v>4270</v>
+        <v>4245</v>
       </c>
       <c r="B52" s="36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C52" s="36" t="n">
         <v>0</v>
@@ -7342,18 +7378,18 @@
     </row>
     <row r="53" ht="15" customHeight="1" s="61">
       <c r="A53" s="36" t="n">
-        <v>4275</v>
+        <v>4250</v>
       </c>
       <c r="B53" s="36" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="C53" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="61">
       <c r="A54" s="36" t="n">
-        <v>4280</v>
+        <v>4255</v>
       </c>
       <c r="B54" s="36" t="n">
         <v>1</v>
@@ -7364,10 +7400,10 @@
     </row>
     <row r="55" ht="15" customHeight="1" s="61">
       <c r="A55" s="36" t="n">
-        <v>4285</v>
+        <v>4260</v>
       </c>
       <c r="B55" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C55" s="36" t="n">
         <v>0</v>
@@ -7375,10 +7411,10 @@
     </row>
     <row r="56" ht="15" customHeight="1" s="61">
       <c r="A56" s="36" t="n">
-        <v>4290</v>
+        <v>4265</v>
       </c>
       <c r="B56" s="36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56" s="36" t="n">
         <v>0</v>
@@ -7386,10 +7422,10 @@
     </row>
     <row r="57" ht="15" customHeight="1" s="61">
       <c r="A57" s="36" t="n">
-        <v>4295</v>
+        <v>4270</v>
       </c>
       <c r="B57" s="36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C57" s="36" t="n">
         <v>0</v>
@@ -7397,18 +7433,18 @@
     </row>
     <row r="58" ht="15" customHeight="1" s="61">
       <c r="A58" s="36" t="n">
-        <v>4300</v>
+        <v>4275</v>
       </c>
       <c r="B58" s="36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C58" s="36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1" s="61">
       <c r="A59" s="36" t="n">
-        <v>4305</v>
+        <v>4280</v>
       </c>
       <c r="B59" s="36" t="n">
         <v>1</v>
@@ -7419,7 +7455,7 @@
     </row>
     <row r="60" ht="15" customHeight="1" s="61">
       <c r="A60" s="36" t="n">
-        <v>4310</v>
+        <v>4285</v>
       </c>
       <c r="B60" s="36" t="n">
         <v>1</v>
@@ -7430,10 +7466,10 @@
     </row>
     <row r="61" ht="15" customHeight="1" s="61">
       <c r="A61" s="36" t="n">
-        <v>4315</v>
+        <v>4290</v>
       </c>
       <c r="B61" s="36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C61" s="36" t="n">
         <v>0</v>
@@ -7441,7 +7477,7 @@
     </row>
     <row r="62" ht="15" customHeight="1" s="61">
       <c r="A62" s="36" t="n">
-        <v>4320</v>
+        <v>4295</v>
       </c>
       <c r="B62" s="36" t="n">
         <v>0</v>
@@ -7452,10 +7488,10 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="61">
       <c r="A63" s="36" t="n">
-        <v>4325</v>
+        <v>4300</v>
       </c>
       <c r="B63" s="36" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C63" s="36" t="n">
         <v>1</v>
@@ -7463,7 +7499,7 @@
     </row>
     <row r="64" ht="15" customHeight="1" s="61">
       <c r="A64" s="36" t="n">
-        <v>4330</v>
+        <v>4305</v>
       </c>
       <c r="B64" s="36" t="n">
         <v>0</v>
@@ -7474,7 +7510,7 @@
     </row>
     <row r="65" ht="15" customHeight="1" s="61">
       <c r="A65" s="36" t="n">
-        <v>4335</v>
+        <v>4310</v>
       </c>
       <c r="B65" s="36" t="n">
         <v>0</v>
@@ -7485,7 +7521,7 @@
     </row>
     <row r="66" ht="15" customHeight="1" s="61">
       <c r="A66" s="36" t="n">
-        <v>4340</v>
+        <v>4315</v>
       </c>
       <c r="B66" s="36" t="n">
         <v>0</v>
@@ -7496,7 +7532,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4345</v>
+        <v>4320</v>
       </c>
       <c r="B67" t="n">
         <v>0</v>
@@ -7507,21 +7543,21 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>4350</v>
+        <v>4325</v>
       </c>
       <c r="B68" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>4355</v>
+        <v>4330</v>
       </c>
       <c r="B69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" t="n">
         <v>0</v>
@@ -7529,7 +7565,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>4360</v>
+        <v>4335</v>
       </c>
       <c r="B70" t="n">
         <v>0</v>
@@ -7540,7 +7576,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>4365</v>
+        <v>4340</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
@@ -7551,7 +7587,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>4370</v>
+        <v>4345</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -7562,10 +7598,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>4375</v>
+        <v>4350</v>
       </c>
       <c r="B73" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C73" t="n">
         <v>0</v>
@@ -7573,7 +7609,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>4380</v>
+        <v>4355</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
@@ -7584,7 +7620,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>4385</v>
+        <v>4360</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -7595,7 +7631,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>4390</v>
+        <v>4365</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
@@ -7606,7 +7642,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>4395</v>
+        <v>4370</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
@@ -7617,10 +7653,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>4400</v>
+        <v>4375</v>
       </c>
       <c r="B78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -7628,7 +7664,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4405</v>
+        <v>4380</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -7639,7 +7675,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>4410</v>
+        <v>4385</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -7650,7 +7686,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>4415</v>
+        <v>4390</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
@@ -7661,7 +7697,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>4420</v>
+        <v>4395</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -7672,10 +7708,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>4425</v>
+        <v>4400</v>
       </c>
       <c r="B83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -7683,7 +7719,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>4430</v>
+        <v>4405</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
@@ -7694,7 +7730,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>4435</v>
+        <v>4410</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
@@ -7705,7 +7741,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>4440</v>
+        <v>4415</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
@@ -7716,7 +7752,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>4445</v>
+        <v>4420</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -7727,10 +7763,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>4450</v>
+        <v>4425</v>
       </c>
       <c r="B88" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -7738,7 +7774,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>4455</v>
+        <v>4430</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -7749,7 +7785,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>4460</v>
+        <v>4435</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
@@ -7760,7 +7796,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>4465</v>
+        <v>4440</v>
       </c>
       <c r="B91" t="n">
         <v>0</v>
@@ -7771,7 +7807,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>4470</v>
+        <v>4445</v>
       </c>
       <c r="B92" t="n">
         <v>0</v>
@@ -7782,10 +7818,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>4475</v>
+        <v>4450</v>
       </c>
       <c r="B93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93" t="n">
         <v>0</v>
@@ -7793,7 +7829,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>4480</v>
+        <v>4455</v>
       </c>
       <c r="B94" t="n">
         <v>0</v>
@@ -7804,7 +7840,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>4485</v>
+        <v>4460</v>
       </c>
       <c r="B95" t="n">
         <v>0</v>
@@ -7815,7 +7851,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>4490</v>
+        <v>4465</v>
       </c>
       <c r="B96" t="n">
         <v>0</v>
@@ -7826,7 +7862,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>4495</v>
+        <v>4470</v>
       </c>
       <c r="B97" t="n">
         <v>0</v>
@@ -7837,10 +7873,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>4500</v>
+        <v>4475</v>
       </c>
       <c r="B98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98" t="n">
         <v>0</v>
@@ -7848,20 +7884,70 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
+        <v>4480</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>4485</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>4490</v>
+      </c>
+      <c r="B101" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>4495</v>
+      </c>
+      <c r="B102" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>4500</v>
+      </c>
+      <c r="B103" t="n">
+        <v>2</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
         <v>4505</v>
       </c>
-      <c r="B99" t="n">
-        <v>0</v>
-      </c>
-      <c r="C99" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100"/>
-    <row r="101"/>
-    <row r="102"/>
-    <row r="103"/>
-    <row r="104"/>
+      <c r="B104" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0</v>
+      </c>
+    </row>
     <row r="105"/>
     <row r="106"/>
     <row r="107"/>
@@ -7969,6 +8055,16 @@
           <t>โซน</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ข้อมูลวันที่ / สัญญา</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-10-07 OG2V6 (Week 2 - OCT 2026)</t>
+        </is>
+      </c>
       <c r="AB1" s="35" t="inlineStr">
         <is>
           <t>Pin score (ตัวช่วย)</t>
@@ -7993,11 +8089,11 @@
         <v/>
       </c>
       <c r="E2" s="39">
-        <f>IF($A2="","",IF(MEDIAN($C$2:$C$152)=0,"",C2/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A2="",$J$12=0),"",C2/$J$12)</f>
         <v/>
       </c>
       <c r="F2" s="38">
-        <f>IF($A2="","",IF(C2&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C2&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A2="","",IF(C2&gt;=2*$J$12,"จุดหนืด",IF(C2&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H2" s="40">
@@ -8036,11 +8132,11 @@
         <v/>
       </c>
       <c r="E3" s="39">
-        <f>IF($A3="","",IF(MEDIAN($C$2:$C$152)=0,"",C3/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A3="",$J$12=0),"",C3/$J$12)</f>
         <v/>
       </c>
       <c r="F3" s="38">
-        <f>IF($A3="","",IF(C3&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C3&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A3="","",IF(C3&gt;=2*$J$12,"จุดหนืด",IF(C3&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H3" s="40">
@@ -8079,11 +8175,11 @@
         <v/>
       </c>
       <c r="E4" s="39">
-        <f>IF($A4="","",IF(MEDIAN($C$2:$C$152)=0,"",C4/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A4="",$J$12=0),"",C4/$J$12)</f>
         <v/>
       </c>
       <c r="F4" s="38">
-        <f>IF($A4="","",IF(C4&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C4&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A4="","",IF(C4&gt;=2*$J$12,"จุดหนืด",IF(C4&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H4" s="40">
@@ -8122,11 +8218,11 @@
         <v/>
       </c>
       <c r="E5" s="39">
-        <f>IF($A5="","",IF(MEDIAN($C$2:$C$152)=0,"",C5/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A5="",$J$12=0),"",C5/$J$12)</f>
         <v/>
       </c>
       <c r="F5" s="38">
-        <f>IF($A5="","",IF(C5&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C5&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A5="","",IF(C5&gt;=2*$J$12,"จุดหนืด",IF(C5&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H5" s="40">
@@ -8165,11 +8261,11 @@
         <v/>
       </c>
       <c r="E6" s="39">
-        <f>IF($A6="","",IF(MEDIAN($C$2:$C$152)=0,"",C6/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A6="",$J$12=0),"",C6/$J$12)</f>
         <v/>
       </c>
       <c r="F6" s="38">
-        <f>IF($A6="","",IF(C6&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C6&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A6="","",IF(C6&gt;=2*$J$12,"จุดหนืด",IF(C6&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H6" s="40">
@@ -8182,7 +8278,7 @@
         </is>
       </c>
       <c r="J6" s="45" t="n">
-        <v>4162.3</v>
+        <v>4212.2</v>
       </c>
       <c r="AB6">
         <f>IF(NOT(ISNUMBER('Gamma Data'!A6)),"",IF((ABS('Gamma Data'!B6)+ABS('Gamma Data'!C6))=0,"",IF(OR(ABS('Gamma Data'!A6-$J$6)&gt;$J$6*$J$26,ABS('Gamma Data'!A6-$J$6)&lt;$J$28),"",(ABS('Gamma Data'!B6)+ABS('Gamma Data'!C6))/MAX(ABS('Gamma Data'!A6-$J$6)/($J$6*0.005),1)+ROW()/1000000000)))</f>
@@ -8207,11 +8303,11 @@
         <v/>
       </c>
       <c r="E7" s="39">
-        <f>IF($A7="","",IF(MEDIAN($C$2:$C$152)=0,"",C7/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A7="",$J$12=0),"",C7/$J$12)</f>
         <v/>
       </c>
       <c r="F7" s="38">
-        <f>IF($A7="","",IF(C7&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C7&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A7="","",IF(C7&gt;=2*$J$12,"จุดหนืด",IF(C7&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H7" s="40">
@@ -8245,11 +8341,11 @@
         <v/>
       </c>
       <c r="E8" s="39">
-        <f>IF($A8="","",IF(MEDIAN($C$2:$C$152)=0,"",C8/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A8="",$J$12=0),"",C8/$J$12)</f>
         <v/>
       </c>
       <c r="F8" s="38">
-        <f>IF($A8="","",IF(C8&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C8&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A8="","",IF(C8&gt;=2*$J$12,"จุดหนืด",IF(C8&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H8" s="40">
@@ -8284,11 +8380,11 @@
         <v/>
       </c>
       <c r="E9" s="39">
-        <f>IF($A9="","",IF(MEDIAN($C$2:$C$152)=0,"",C9/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A9="",$J$12=0),"",C9/$J$12)</f>
         <v/>
       </c>
       <c r="F9" s="38">
-        <f>IF($A9="","",IF(C9&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C9&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A9="","",IF(C9&gt;=2*$J$12,"จุดหนืด",IF(C9&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H9" s="40">
@@ -8327,11 +8423,11 @@
         <v/>
       </c>
       <c r="E10" s="39">
-        <f>IF($A10="","",IF(MEDIAN($C$2:$C$152)=0,"",C10/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A10="",$J$12=0),"",C10/$J$12)</f>
         <v/>
       </c>
       <c r="F10" s="38">
-        <f>IF($A10="","",IF(C10&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C10&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A10="","",IF(C10&gt;=2*$J$12,"จุดหนืด",IF(C10&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H10" s="40">
@@ -8370,11 +8466,11 @@
         <v/>
       </c>
       <c r="E11" s="39">
-        <f>IF($A11="","",IF(MEDIAN($C$2:$C$152)=0,"",C11/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A11="",$J$12=0),"",C11/$J$12)</f>
         <v/>
       </c>
       <c r="F11" s="38">
-        <f>IF($A11="","",IF(C11&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C11&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A11="","",IF(C11&gt;=2*$J$12,"จุดหนืด",IF(C11&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H11" s="40">
@@ -8413,11 +8509,11 @@
         <v/>
       </c>
       <c r="E12" s="39">
-        <f>IF($A12="","",IF(MEDIAN($C$2:$C$152)=0,"",C12/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A12="",$J$12=0),"",C12/$J$12)</f>
         <v/>
       </c>
       <c r="F12" s="38">
-        <f>IF($A12="","",IF(C12&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C12&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A12="","",IF(C12&gt;=2*$J$12,"จุดหนืด",IF(C12&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H12" s="40">
@@ -8426,11 +8522,11 @@
       </c>
       <c r="I12" s="41" t="inlineStr">
         <is>
-          <t>ค่ากลาง Gross</t>
+          <t>ค่ากลาง Gross (strike ที่มี gamma, ±J26 ของราคา)</t>
         </is>
       </c>
       <c r="J12" s="49">
-        <f t="array" ref="J12">MEDIAN(IF(ISNUMBER('Gamma Data'!$A$2:$A$152),ABS('Gamma Data'!$B$2:$B$152)+ABS('Gamma Data'!$C$2:$C$152)))</f>
+        <f t="array" ref="J12">IFERROR(MEDIAN(IF(ISNUMBER('Gamma Data'!$A$2:$A$152)*((ABS('Gamma Data'!$B$2:$B$152)+ABS('Gamma Data'!$C$2:$C$152))&gt;0)*(ABS('Gamma Data'!$A$2:$A$152-$J$6)&lt;=$J$6*$J$26),(ABS('Gamma Data'!$B$2:$B$152)+ABS('Gamma Data'!$C$2:$C$152)))),0)</f>
         <v/>
       </c>
       <c r="AB12">
@@ -8456,11 +8552,11 @@
         <v/>
       </c>
       <c r="E13" s="39">
-        <f>IF($A13="","",IF(MEDIAN($C$2:$C$152)=0,"",C13/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A13="",$J$12=0),"",C13/$J$12)</f>
         <v/>
       </c>
       <c r="F13" s="38">
-        <f>IF($A13="","",IF(C13&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C13&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A13="","",IF(C13&gt;=2*$J$12,"จุดหนืด",IF(C13&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H13" s="40">
@@ -8494,11 +8590,11 @@
         <v/>
       </c>
       <c r="E14" s="39">
-        <f>IF($A14="","",IF(MEDIAN($C$2:$C$152)=0,"",C14/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A14="",$J$12=0),"",C14/$J$12)</f>
         <v/>
       </c>
       <c r="F14" s="38">
-        <f>IF($A14="","",IF(C14&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C14&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A14="","",IF(C14&gt;=2*$J$12,"จุดหนืด",IF(C14&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H14" s="40">
@@ -8533,11 +8629,11 @@
         <v/>
       </c>
       <c r="E15" s="39">
-        <f>IF($A15="","",IF(MEDIAN($C$2:$C$152)=0,"",C15/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A15="",$J$12=0),"",C15/$J$12)</f>
         <v/>
       </c>
       <c r="F15" s="38">
-        <f>IF($A15="","",IF(C15&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C15&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A15="","",IF(C15&gt;=2*$J$12,"จุดหนืด",IF(C15&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H15" s="40">
@@ -8576,11 +8672,11 @@
         <v/>
       </c>
       <c r="E16" s="39">
-        <f>IF($A16="","",IF(MEDIAN($C$2:$C$152)=0,"",C16/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A16="",$J$12=0),"",C16/$J$12)</f>
         <v/>
       </c>
       <c r="F16" s="38">
-        <f>IF($A16="","",IF(C16&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C16&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A16="","",IF(C16&gt;=2*$J$12,"จุดหนืด",IF(C16&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H16" s="40">
@@ -8619,11 +8715,11 @@
         <v/>
       </c>
       <c r="E17" s="39">
-        <f>IF($A17="","",IF(MEDIAN($C$2:$C$152)=0,"",C17/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A17="",$J$12=0),"",C17/$J$12)</f>
         <v/>
       </c>
       <c r="F17" s="38">
-        <f>IF($A17="","",IF(C17&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C17&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A17="","",IF(C17&gt;=2*$J$12,"จุดหนืด",IF(C17&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H17" s="40">
@@ -8662,11 +8758,11 @@
         <v/>
       </c>
       <c r="E18" s="39">
-        <f>IF($A18="","",IF(MEDIAN($C$2:$C$152)=0,"",C18/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A18="",$J$12=0),"",C18/$J$12)</f>
         <v/>
       </c>
       <c r="F18" s="38">
-        <f>IF($A18="","",IF(C18&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C18&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A18="","",IF(C18&gt;=2*$J$12,"จุดหนืด",IF(C18&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H18" s="40">
@@ -8705,11 +8801,11 @@
         <v/>
       </c>
       <c r="E19" s="39">
-        <f>IF($A19="","",IF(MEDIAN($C$2:$C$152)=0,"",C19/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A19="",$J$12=0),"",C19/$J$12)</f>
         <v/>
       </c>
       <c r="F19" s="38">
-        <f>IF($A19="","",IF(C19&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C19&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A19="","",IF(C19&gt;=2*$J$12,"จุดหนืด",IF(C19&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H19" s="40">
@@ -8743,11 +8839,11 @@
         <v/>
       </c>
       <c r="E20" s="39">
-        <f>IF($A20="","",IF(MEDIAN($C$2:$C$152)=0,"",C20/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A20="",$J$12=0),"",C20/$J$12)</f>
         <v/>
       </c>
       <c r="F20" s="38">
-        <f>IF($A20="","",IF(C20&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C20&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A20="","",IF(C20&gt;=2*$J$12,"จุดหนืด",IF(C20&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H20" s="40">
@@ -8777,11 +8873,11 @@
         <v/>
       </c>
       <c r="E21" s="39">
-        <f>IF($A21="","",IF(MEDIAN($C$2:$C$152)=0,"",C21/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A21="",$J$12=0),"",C21/$J$12)</f>
         <v/>
       </c>
       <c r="F21" s="38">
-        <f>IF($A21="","",IF(C21&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C21&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A21="","",IF(C21&gt;=2*$J$12,"จุดหนืด",IF(C21&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H21" s="40">
@@ -8811,11 +8907,11 @@
         <v/>
       </c>
       <c r="E22" s="39">
-        <f>IF($A22="","",IF(MEDIAN($C$2:$C$152)=0,"",C22/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A22="",$J$12=0),"",C22/$J$12)</f>
         <v/>
       </c>
       <c r="F22" s="38">
-        <f>IF($A22="","",IF(C22&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C22&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A22="","",IF(C22&gt;=2*$J$12,"จุดหนืด",IF(C22&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H22" s="40">
@@ -8845,11 +8941,11 @@
         <v/>
       </c>
       <c r="E23" s="39">
-        <f>IF($A23="","",IF(MEDIAN($C$2:$C$152)=0,"",C23/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A23="",$J$12=0),"",C23/$J$12)</f>
         <v/>
       </c>
       <c r="F23" s="38">
-        <f>IF($A23="","",IF(C23&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C23&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A23="","",IF(C23&gt;=2*$J$12,"จุดหนืด",IF(C23&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H23" s="40">
@@ -8879,11 +8975,11 @@
         <v/>
       </c>
       <c r="E24" s="39">
-        <f>IF($A24="","",IF(MEDIAN($C$2:$C$152)=0,"",C24/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A24="",$J$12=0),"",C24/$J$12)</f>
         <v/>
       </c>
       <c r="F24" s="38">
-        <f>IF($A24="","",IF(C24&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C24&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A24="","",IF(C24&gt;=2*$J$12,"จุดหนืด",IF(C24&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H24" s="40">
@@ -8913,11 +9009,11 @@
         <v/>
       </c>
       <c r="E25" s="39">
-        <f>IF($A25="","",IF(MEDIAN($C$2:$C$152)=0,"",C25/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A25="",$J$12=0),"",C25/$J$12)</f>
         <v/>
       </c>
       <c r="F25" s="38">
-        <f>IF($A25="","",IF(C25&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C25&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A25="","",IF(C25&gt;=2*$J$12,"จุดหนืด",IF(C25&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H25" s="40">
@@ -8952,11 +9048,11 @@
         <v/>
       </c>
       <c r="E26" s="39">
-        <f>IF($A26="","",IF(MEDIAN($C$2:$C$152)=0,"",C26/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A26="",$J$12=0),"",C26/$J$12)</f>
         <v/>
       </c>
       <c r="F26" s="38">
-        <f>IF($A26="","",IF(C26&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C26&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A26="","",IF(C26&gt;=2*$J$12,"จุดหนืด",IF(C26&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H26" s="40">
@@ -8994,11 +9090,11 @@
         <v/>
       </c>
       <c r="E27" s="39">
-        <f>IF($A27="","",IF(MEDIAN($C$2:$C$152)=0,"",C27/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A27="",$J$12=0),"",C27/$J$12)</f>
         <v/>
       </c>
       <c r="F27" s="38">
-        <f>IF($A27="","",IF(C27&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C27&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A27="","",IF(C27&gt;=2*$J$12,"จุดหนืด",IF(C27&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H27" s="40">
@@ -9037,11 +9133,11 @@
         <v/>
       </c>
       <c r="E28" s="39">
-        <f>IF($A28="","",IF(MEDIAN($C$2:$C$152)=0,"",C28/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A28="",$J$12=0),"",C28/$J$12)</f>
         <v/>
       </c>
       <c r="F28" s="38">
-        <f>IF($A28="","",IF(C28&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C28&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A28="","",IF(C28&gt;=2*$J$12,"จุดหนืด",IF(C28&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H28" s="40">
@@ -9079,11 +9175,11 @@
         <v/>
       </c>
       <c r="E29" s="39">
-        <f>IF($A29="","",IF(MEDIAN($C$2:$C$152)=0,"",C29/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A29="",$J$12=0),"",C29/$J$12)</f>
         <v/>
       </c>
       <c r="F29" s="38">
-        <f>IF($A29="","",IF(C29&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C29&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A29="","",IF(C29&gt;=2*$J$12,"จุดหนืด",IF(C29&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H29" s="40">
@@ -9138,11 +9234,11 @@
         <v/>
       </c>
       <c r="E30" s="39">
-        <f>IF($A30="","",IF(MEDIAN($C$2:$C$152)=0,"",C30/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A30="",$J$12=0),"",C30/$J$12)</f>
         <v/>
       </c>
       <c r="F30" s="38">
-        <f>IF($A30="","",IF(C30&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C30&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A30="","",IF(C30&gt;=2*$J$12,"จุดหนืด",IF(C30&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H30" s="40">
@@ -9191,11 +9287,11 @@
         <v/>
       </c>
       <c r="E31" s="39">
-        <f>IF($A31="","",IF(MEDIAN($C$2:$C$152)=0,"",C31/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A31="",$J$12=0),"",C31/$J$12)</f>
         <v/>
       </c>
       <c r="F31" s="38">
-        <f>IF($A31="","",IF(C31&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C31&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A31="","",IF(C31&gt;=2*$J$12,"จุดหนืด",IF(C31&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H31" s="40">
@@ -9244,11 +9340,11 @@
         <v/>
       </c>
       <c r="E32" s="39">
-        <f>IF($A32="","",IF(MEDIAN($C$2:$C$152)=0,"",C32/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A32="",$J$12=0),"",C32/$J$12)</f>
         <v/>
       </c>
       <c r="F32" s="38">
-        <f>IF($A32="","",IF(C32&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C32&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A32="","",IF(C32&gt;=2*$J$12,"จุดหนืด",IF(C32&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H32" s="40">
@@ -9297,11 +9393,11 @@
         <v/>
       </c>
       <c r="E33" s="39">
-        <f>IF($A33="","",IF(MEDIAN($C$2:$C$152)=0,"",C33/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A33="",$J$12=0),"",C33/$J$12)</f>
         <v/>
       </c>
       <c r="F33" s="38">
-        <f>IF($A33="","",IF(C33&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C33&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A33="","",IF(C33&gt;=2*$J$12,"จุดหนืด",IF(C33&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H33" s="40">
@@ -9350,11 +9446,11 @@
         <v/>
       </c>
       <c r="E34" s="39">
-        <f>IF($A34="","",IF(MEDIAN($C$2:$C$152)=0,"",C34/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A34="",$J$12=0),"",C34/$J$12)</f>
         <v/>
       </c>
       <c r="F34" s="38">
-        <f>IF($A34="","",IF(C34&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C34&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A34="","",IF(C34&gt;=2*$J$12,"จุดหนืด",IF(C34&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H34" s="40">
@@ -9403,11 +9499,11 @@
         <v/>
       </c>
       <c r="E35" s="39">
-        <f>IF($A35="","",IF(MEDIAN($C$2:$C$152)=0,"",C35/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A35="",$J$12=0),"",C35/$J$12)</f>
         <v/>
       </c>
       <c r="F35" s="38">
-        <f>IF($A35="","",IF(C35&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C35&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A35="","",IF(C35&gt;=2*$J$12,"จุดหนืด",IF(C35&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H35" s="40">
@@ -9437,11 +9533,11 @@
         <v/>
       </c>
       <c r="E36" s="39">
-        <f>IF($A36="","",IF(MEDIAN($C$2:$C$152)=0,"",C36/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A36="",$J$12=0),"",C36/$J$12)</f>
         <v/>
       </c>
       <c r="F36" s="38">
-        <f>IF($A36="","",IF(C36&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C36&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A36="","",IF(C36&gt;=2*$J$12,"จุดหนืด",IF(C36&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H36" s="40">
@@ -9475,11 +9571,11 @@
         <v/>
       </c>
       <c r="E37" s="39">
-        <f>IF($A37="","",IF(MEDIAN($C$2:$C$152)=0,"",C37/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A37="",$J$12=0),"",C37/$J$12)</f>
         <v/>
       </c>
       <c r="F37" s="38">
-        <f>IF($A37="","",IF(C37&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C37&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A37="","",IF(C37&gt;=2*$J$12,"จุดหนืด",IF(C37&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H37" s="40">
@@ -9513,11 +9609,11 @@
         <v/>
       </c>
       <c r="E38" s="39">
-        <f>IF($A38="","",IF(MEDIAN($C$2:$C$152)=0,"",C38/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A38="",$J$12=0),"",C38/$J$12)</f>
         <v/>
       </c>
       <c r="F38" s="38">
-        <f>IF($A38="","",IF(C38&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C38&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A38="","",IF(C38&gt;=2*$J$12,"จุดหนืด",IF(C38&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H38" s="40">
@@ -9551,11 +9647,11 @@
         <v/>
       </c>
       <c r="E39" s="39">
-        <f>IF($A39="","",IF(MEDIAN($C$2:$C$152)=0,"",C39/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A39="",$J$12=0),"",C39/$J$12)</f>
         <v/>
       </c>
       <c r="F39" s="38">
-        <f>IF($A39="","",IF(C39&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C39&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A39="","",IF(C39&gt;=2*$J$12,"จุดหนืด",IF(C39&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H39" s="40">
@@ -9589,11 +9685,11 @@
         <v/>
       </c>
       <c r="E40" s="39">
-        <f>IF($A40="","",IF(MEDIAN($C$2:$C$152)=0,"",C40/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A40="",$J$12=0),"",C40/$J$12)</f>
         <v/>
       </c>
       <c r="F40" s="38">
-        <f>IF($A40="","",IF(C40&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C40&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A40="","",IF(C40&gt;=2*$J$12,"จุดหนืด",IF(C40&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H40" s="40">
@@ -9627,11 +9723,11 @@
         <v/>
       </c>
       <c r="E41" s="39">
-        <f>IF($A41="","",IF(MEDIAN($C$2:$C$152)=0,"",C41/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A41="",$J$12=0),"",C41/$J$12)</f>
         <v/>
       </c>
       <c r="F41" s="38">
-        <f>IF($A41="","",IF(C41&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C41&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A41="","",IF(C41&gt;=2*$J$12,"จุดหนืด",IF(C41&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H41" s="40">
@@ -9665,11 +9761,11 @@
         <v/>
       </c>
       <c r="E42" s="39">
-        <f>IF($A42="","",IF(MEDIAN($C$2:$C$152)=0,"",C42/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A42="",$J$12=0),"",C42/$J$12)</f>
         <v/>
       </c>
       <c r="F42" s="38">
-        <f>IF($A42="","",IF(C42&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C42&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A42="","",IF(C42&gt;=2*$J$12,"จุดหนืด",IF(C42&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H42" s="40">
@@ -9699,11 +9795,11 @@
         <v/>
       </c>
       <c r="E43" s="39">
-        <f>IF($A43="","",IF(MEDIAN($C$2:$C$152)=0,"",C43/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A43="",$J$12=0),"",C43/$J$12)</f>
         <v/>
       </c>
       <c r="F43" s="38">
-        <f>IF($A43="","",IF(C43&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C43&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A43="","",IF(C43&gt;=2*$J$12,"จุดหนืด",IF(C43&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H43" s="40">
@@ -9733,11 +9829,11 @@
         <v/>
       </c>
       <c r="E44" s="39">
-        <f>IF($A44="","",IF(MEDIAN($C$2:$C$152)=0,"",C44/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A44="",$J$12=0),"",C44/$J$12)</f>
         <v/>
       </c>
       <c r="F44" s="38">
-        <f>IF($A44="","",IF(C44&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C44&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A44="","",IF(C44&gt;=2*$J$12,"จุดหนืด",IF(C44&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H44" s="40">
@@ -9767,11 +9863,11 @@
         <v/>
       </c>
       <c r="E45" s="39">
-        <f>IF($A45="","",IF(MEDIAN($C$2:$C$152)=0,"",C45/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A45="",$J$12=0),"",C45/$J$12)</f>
         <v/>
       </c>
       <c r="F45" s="38">
-        <f>IF($A45="","",IF(C45&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C45&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A45="","",IF(C45&gt;=2*$J$12,"จุดหนืด",IF(C45&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H45" s="40">
@@ -9801,11 +9897,11 @@
         <v/>
       </c>
       <c r="E46" s="39">
-        <f>IF($A46="","",IF(MEDIAN($C$2:$C$152)=0,"",C46/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A46="",$J$12=0),"",C46/$J$12)</f>
         <v/>
       </c>
       <c r="F46" s="38">
-        <f>IF($A46="","",IF(C46&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C46&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A46="","",IF(C46&gt;=2*$J$12,"จุดหนืด",IF(C46&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H46" s="40">
@@ -9835,11 +9931,11 @@
         <v/>
       </c>
       <c r="E47" s="39">
-        <f>IF($A47="","",IF(MEDIAN($C$2:$C$152)=0,"",C47/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A47="",$J$12=0),"",C47/$J$12)</f>
         <v/>
       </c>
       <c r="F47" s="38">
-        <f>IF($A47="","",IF(C47&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C47&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A47="","",IF(C47&gt;=2*$J$12,"จุดหนืด",IF(C47&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H47" s="40">
@@ -9869,11 +9965,11 @@
         <v/>
       </c>
       <c r="E48" s="39">
-        <f>IF($A48="","",IF(MEDIAN($C$2:$C$152)=0,"",C48/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A48="",$J$12=0),"",C48/$J$12)</f>
         <v/>
       </c>
       <c r="F48" s="38">
-        <f>IF($A48="","",IF(C48&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C48&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A48="","",IF(C48&gt;=2*$J$12,"จุดหนืด",IF(C48&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H48" s="40">
@@ -9903,11 +9999,11 @@
         <v/>
       </c>
       <c r="E49" s="39">
-        <f>IF($A49="","",IF(MEDIAN($C$2:$C$152)=0,"",C49/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A49="",$J$12=0),"",C49/$J$12)</f>
         <v/>
       </c>
       <c r="F49" s="38">
-        <f>IF($A49="","",IF(C49&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C49&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A49="","",IF(C49&gt;=2*$J$12,"จุดหนืด",IF(C49&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H49" s="40">
@@ -9937,11 +10033,11 @@
         <v/>
       </c>
       <c r="E50" s="39">
-        <f>IF($A50="","",IF(MEDIAN($C$2:$C$152)=0,"",C50/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A50="",$J$12=0),"",C50/$J$12)</f>
         <v/>
       </c>
       <c r="F50" s="38">
-        <f>IF($A50="","",IF(C50&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C50&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A50="","",IF(C50&gt;=2*$J$12,"จุดหนืด",IF(C50&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H50" s="40">
@@ -9971,11 +10067,11 @@
         <v/>
       </c>
       <c r="E51" s="39">
-        <f>IF($A51="","",IF(MEDIAN($C$2:$C$152)=0,"",C51/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A51="",$J$12=0),"",C51/$J$12)</f>
         <v/>
       </c>
       <c r="F51" s="38">
-        <f>IF($A51="","",IF(C51&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C51&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A51="","",IF(C51&gt;=2*$J$12,"จุดหนืด",IF(C51&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H51" s="40">
@@ -10005,11 +10101,11 @@
         <v/>
       </c>
       <c r="E52" s="39">
-        <f>IF($A52="","",IF(MEDIAN($C$2:$C$152)=0,"",C52/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A52="",$J$12=0),"",C52/$J$12)</f>
         <v/>
       </c>
       <c r="F52" s="38">
-        <f>IF($A52="","",IF(C52&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C52&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A52="","",IF(C52&gt;=2*$J$12,"จุดหนืด",IF(C52&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H52" s="40">
@@ -10039,11 +10135,11 @@
         <v/>
       </c>
       <c r="E53" s="39">
-        <f>IF($A53="","",IF(MEDIAN($C$2:$C$152)=0,"",C53/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A53="",$J$12=0),"",C53/$J$12)</f>
         <v/>
       </c>
       <c r="F53" s="38">
-        <f>IF($A53="","",IF(C53&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C53&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A53="","",IF(C53&gt;=2*$J$12,"จุดหนืด",IF(C53&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H53" s="40">
@@ -10073,11 +10169,11 @@
         <v/>
       </c>
       <c r="E54" s="39">
-        <f>IF($A54="","",IF(MEDIAN($C$2:$C$152)=0,"",C54/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A54="",$J$12=0),"",C54/$J$12)</f>
         <v/>
       </c>
       <c r="F54" s="38">
-        <f>IF($A54="","",IF(C54&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C54&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A54="","",IF(C54&gt;=2*$J$12,"จุดหนืด",IF(C54&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H54" s="40">
@@ -10107,11 +10203,11 @@
         <v/>
       </c>
       <c r="E55" s="39">
-        <f>IF($A55="","",IF(MEDIAN($C$2:$C$152)=0,"",C55/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A55="",$J$12=0),"",C55/$J$12)</f>
         <v/>
       </c>
       <c r="F55" s="38">
-        <f>IF($A55="","",IF(C55&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C55&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A55="","",IF(C55&gt;=2*$J$12,"จุดหนืด",IF(C55&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H55" s="40">
@@ -10141,11 +10237,11 @@
         <v/>
       </c>
       <c r="E56" s="39">
-        <f>IF($A56="","",IF(MEDIAN($C$2:$C$152)=0,"",C56/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A56="",$J$12=0),"",C56/$J$12)</f>
         <v/>
       </c>
       <c r="F56" s="38">
-        <f>IF($A56="","",IF(C56&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C56&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A56="","",IF(C56&gt;=2*$J$12,"จุดหนืด",IF(C56&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H56" s="40">
@@ -10175,11 +10271,11 @@
         <v/>
       </c>
       <c r="E57" s="39">
-        <f>IF($A57="","",IF(MEDIAN($C$2:$C$152)=0,"",C57/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A57="",$J$12=0),"",C57/$J$12)</f>
         <v/>
       </c>
       <c r="F57" s="38">
-        <f>IF($A57="","",IF(C57&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C57&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A57="","",IF(C57&gt;=2*$J$12,"จุดหนืด",IF(C57&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H57" s="40">
@@ -10209,11 +10305,11 @@
         <v/>
       </c>
       <c r="E58" s="39">
-        <f>IF($A58="","",IF(MEDIAN($C$2:$C$152)=0,"",C58/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A58="",$J$12=0),"",C58/$J$12)</f>
         <v/>
       </c>
       <c r="F58" s="38">
-        <f>IF($A58="","",IF(C58&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C58&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A58="","",IF(C58&gt;=2*$J$12,"จุดหนืด",IF(C58&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H58" s="40">
@@ -10243,11 +10339,11 @@
         <v/>
       </c>
       <c r="E59" s="39">
-        <f>IF($A59="","",IF(MEDIAN($C$2:$C$152)=0,"",C59/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A59="",$J$12=0),"",C59/$J$12)</f>
         <v/>
       </c>
       <c r="F59" s="38">
-        <f>IF($A59="","",IF(C59&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C59&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A59="","",IF(C59&gt;=2*$J$12,"จุดหนืด",IF(C59&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H59" s="40">
@@ -10277,11 +10373,11 @@
         <v/>
       </c>
       <c r="E60" s="39">
-        <f>IF($A60="","",IF(MEDIAN($C$2:$C$152)=0,"",C60/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A60="",$J$12=0),"",C60/$J$12)</f>
         <v/>
       </c>
       <c r="F60" s="38">
-        <f>IF($A60="","",IF(C60&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C60&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A60="","",IF(C60&gt;=2*$J$12,"จุดหนืด",IF(C60&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H60" s="40">
@@ -10311,11 +10407,11 @@
         <v/>
       </c>
       <c r="E61" s="39">
-        <f>IF($A61="","",IF(MEDIAN($C$2:$C$152)=0,"",C61/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A61="",$J$12=0),"",C61/$J$12)</f>
         <v/>
       </c>
       <c r="F61" s="38">
-        <f>IF($A61="","",IF(C61&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C61&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A61="","",IF(C61&gt;=2*$J$12,"จุดหนืด",IF(C61&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H61" s="40">
@@ -10345,11 +10441,11 @@
         <v/>
       </c>
       <c r="E62" s="39">
-        <f>IF($A62="","",IF(MEDIAN($C$2:$C$152)=0,"",C62/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A62="",$J$12=0),"",C62/$J$12)</f>
         <v/>
       </c>
       <c r="F62" s="38">
-        <f>IF($A62="","",IF(C62&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C62&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A62="","",IF(C62&gt;=2*$J$12,"จุดหนืด",IF(C62&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H62" s="40">
@@ -10379,11 +10475,11 @@
         <v/>
       </c>
       <c r="E63" s="39">
-        <f>IF($A63="","",IF(MEDIAN($C$2:$C$152)=0,"",C63/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A63="",$J$12=0),"",C63/$J$12)</f>
         <v/>
       </c>
       <c r="F63" s="38">
-        <f>IF($A63="","",IF(C63&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C63&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A63="","",IF(C63&gt;=2*$J$12,"จุดหนืด",IF(C63&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H63">
@@ -10413,11 +10509,11 @@
         <v/>
       </c>
       <c r="E64" s="39">
-        <f>IF($A64="","",IF(MEDIAN($C$2:$C$152)=0,"",C64/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A64="",$J$12=0),"",C64/$J$12)</f>
         <v/>
       </c>
       <c r="F64" s="38">
-        <f>IF($A64="","",IF(C64&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C64&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A64="","",IF(C64&gt;=2*$J$12,"จุดหนืด",IF(C64&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H64">
@@ -10447,11 +10543,11 @@
         <v/>
       </c>
       <c r="E65" s="39">
-        <f>IF($A65="","",IF(MEDIAN($C$2:$C$152)=0,"",C65/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A65="",$J$12=0),"",C65/$J$12)</f>
         <v/>
       </c>
       <c r="F65" s="38">
-        <f>IF($A65="","",IF(C65&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C65&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A65="","",IF(C65&gt;=2*$J$12,"จุดหนืด",IF(C65&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H65">
@@ -10481,11 +10577,11 @@
         <v/>
       </c>
       <c r="E66" s="39">
-        <f>IF($A66="","",IF(MEDIAN($C$2:$C$152)=0,"",C66/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A66="",$J$12=0),"",C66/$J$12)</f>
         <v/>
       </c>
       <c r="F66" s="38">
-        <f>IF($A66="","",IF(C66&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C66&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A66="","",IF(C66&gt;=2*$J$12,"จุดหนืด",IF(C66&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H66">
@@ -10515,11 +10611,11 @@
         <v/>
       </c>
       <c r="E67" s="39">
-        <f>IF($A67="","",IF(MEDIAN($C$2:$C$152)=0,"",C67/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A67="",$J$12=0),"",C67/$J$12)</f>
         <v/>
       </c>
       <c r="F67" s="38">
-        <f>IF($A67="","",IF(C67&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C67&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A67="","",IF(C67&gt;=2*$J$12,"จุดหนืด",IF(C67&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H67">
@@ -10549,11 +10645,11 @@
         <v/>
       </c>
       <c r="E68" s="39">
-        <f>IF($A68="","",IF(MEDIAN($C$2:$C$152)=0,"",C68/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A68="",$J$12=0),"",C68/$J$12)</f>
         <v/>
       </c>
       <c r="F68" s="38">
-        <f>IF($A68="","",IF(C68&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C68&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A68="","",IF(C68&gt;=2*$J$12,"จุดหนืด",IF(C68&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H68">
@@ -10583,11 +10679,11 @@
         <v/>
       </c>
       <c r="E69" s="39">
-        <f>IF($A69="","",IF(MEDIAN($C$2:$C$152)=0,"",C69/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A69="",$J$12=0),"",C69/$J$12)</f>
         <v/>
       </c>
       <c r="F69" s="38">
-        <f>IF($A69="","",IF(C69&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C69&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A69="","",IF(C69&gt;=2*$J$12,"จุดหนืด",IF(C69&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H69">
@@ -10617,11 +10713,11 @@
         <v/>
       </c>
       <c r="E70" s="39">
-        <f>IF($A70="","",IF(MEDIAN($C$2:$C$152)=0,"",C70/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A70="",$J$12=0),"",C70/$J$12)</f>
         <v/>
       </c>
       <c r="F70" s="38">
-        <f>IF($A70="","",IF(C70&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C70&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A70="","",IF(C70&gt;=2*$J$12,"จุดหนืด",IF(C70&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H70">
@@ -10651,11 +10747,11 @@
         <v/>
       </c>
       <c r="E71" s="39">
-        <f>IF($A71="","",IF(MEDIAN($C$2:$C$152)=0,"",C71/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A71="",$J$12=0),"",C71/$J$12)</f>
         <v/>
       </c>
       <c r="F71" s="38">
-        <f>IF($A71="","",IF(C71&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C71&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A71="","",IF(C71&gt;=2*$J$12,"จุดหนืด",IF(C71&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H71">
@@ -10685,11 +10781,11 @@
         <v/>
       </c>
       <c r="E72" s="39">
-        <f>IF($A72="","",IF(MEDIAN($C$2:$C$152)=0,"",C72/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A72="",$J$12=0),"",C72/$J$12)</f>
         <v/>
       </c>
       <c r="F72" s="38">
-        <f>IF($A72="","",IF(C72&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C72&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A72="","",IF(C72&gt;=2*$J$12,"จุดหนืด",IF(C72&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H72">
@@ -10719,11 +10815,11 @@
         <v/>
       </c>
       <c r="E73" s="39">
-        <f>IF($A73="","",IF(MEDIAN($C$2:$C$152)=0,"",C73/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A73="",$J$12=0),"",C73/$J$12)</f>
         <v/>
       </c>
       <c r="F73" s="38">
-        <f>IF($A73="","",IF(C73&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C73&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A73="","",IF(C73&gt;=2*$J$12,"จุดหนืด",IF(C73&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H73">
@@ -10753,11 +10849,11 @@
         <v/>
       </c>
       <c r="E74" s="39">
-        <f>IF($A74="","",IF(MEDIAN($C$2:$C$152)=0,"",C74/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A74="",$J$12=0),"",C74/$J$12)</f>
         <v/>
       </c>
       <c r="F74" s="38">
-        <f>IF($A74="","",IF(C74&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C74&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A74="","",IF(C74&gt;=2*$J$12,"จุดหนืด",IF(C74&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H74">
@@ -10787,11 +10883,11 @@
         <v/>
       </c>
       <c r="E75" s="39">
-        <f>IF($A75="","",IF(MEDIAN($C$2:$C$152)=0,"",C75/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A75="",$J$12=0),"",C75/$J$12)</f>
         <v/>
       </c>
       <c r="F75" s="38">
-        <f>IF($A75="","",IF(C75&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C75&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A75="","",IF(C75&gt;=2*$J$12,"จุดหนืด",IF(C75&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H75">
@@ -10821,11 +10917,11 @@
         <v/>
       </c>
       <c r="E76" s="39">
-        <f>IF($A76="","",IF(MEDIAN($C$2:$C$152)=0,"",C76/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A76="",$J$12=0),"",C76/$J$12)</f>
         <v/>
       </c>
       <c r="F76" s="38">
-        <f>IF($A76="","",IF(C76&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C76&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A76="","",IF(C76&gt;=2*$J$12,"จุดหนืด",IF(C76&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H76">
@@ -10855,11 +10951,11 @@
         <v/>
       </c>
       <c r="E77" s="39">
-        <f>IF($A77="","",IF(MEDIAN($C$2:$C$152)=0,"",C77/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A77="",$J$12=0),"",C77/$J$12)</f>
         <v/>
       </c>
       <c r="F77" s="38">
-        <f>IF($A77="","",IF(C77&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C77&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A77="","",IF(C77&gt;=2*$J$12,"จุดหนืด",IF(C77&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H77">
@@ -10889,11 +10985,11 @@
         <v/>
       </c>
       <c r="E78" s="39">
-        <f>IF($A78="","",IF(MEDIAN($C$2:$C$152)=0,"",C78/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A78="",$J$12=0),"",C78/$J$12)</f>
         <v/>
       </c>
       <c r="F78" s="38">
-        <f>IF($A78="","",IF(C78&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C78&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A78="","",IF(C78&gt;=2*$J$12,"จุดหนืด",IF(C78&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H78">
@@ -10923,11 +11019,11 @@
         <v/>
       </c>
       <c r="E79" s="39">
-        <f>IF($A79="","",IF(MEDIAN($C$2:$C$152)=0,"",C79/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A79="",$J$12=0),"",C79/$J$12)</f>
         <v/>
       </c>
       <c r="F79" s="38">
-        <f>IF($A79="","",IF(C79&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C79&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A79="","",IF(C79&gt;=2*$J$12,"จุดหนืด",IF(C79&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H79">
@@ -10957,11 +11053,11 @@
         <v/>
       </c>
       <c r="E80" s="39">
-        <f>IF($A80="","",IF(MEDIAN($C$2:$C$152)=0,"",C80/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A80="",$J$12=0),"",C80/$J$12)</f>
         <v/>
       </c>
       <c r="F80" s="38">
-        <f>IF($A80="","",IF(C80&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C80&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A80="","",IF(C80&gt;=2*$J$12,"จุดหนืด",IF(C80&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H80">
@@ -10991,11 +11087,11 @@
         <v/>
       </c>
       <c r="E81" s="39">
-        <f>IF($A81="","",IF(MEDIAN($C$2:$C$152)=0,"",C81/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A81="",$J$12=0),"",C81/$J$12)</f>
         <v/>
       </c>
       <c r="F81" s="38">
-        <f>IF($A81="","",IF(C81&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C81&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A81="","",IF(C81&gt;=2*$J$12,"จุดหนืด",IF(C81&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H81">
@@ -11025,11 +11121,11 @@
         <v/>
       </c>
       <c r="E82" s="39">
-        <f>IF($A82="","",IF(MEDIAN($C$2:$C$152)=0,"",C82/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A82="",$J$12=0),"",C82/$J$12)</f>
         <v/>
       </c>
       <c r="F82" s="38">
-        <f>IF($A82="","",IF(C82&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C82&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A82="","",IF(C82&gt;=2*$J$12,"จุดหนืด",IF(C82&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H82">
@@ -11059,11 +11155,11 @@
         <v/>
       </c>
       <c r="E83" s="39">
-        <f>IF($A83="","",IF(MEDIAN($C$2:$C$152)=0,"",C83/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A83="",$J$12=0),"",C83/$J$12)</f>
         <v/>
       </c>
       <c r="F83" s="38">
-        <f>IF($A83="","",IF(C83&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C83&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A83="","",IF(C83&gt;=2*$J$12,"จุดหนืด",IF(C83&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H83">
@@ -11093,11 +11189,11 @@
         <v/>
       </c>
       <c r="E84" s="39">
-        <f>IF($A84="","",IF(MEDIAN($C$2:$C$152)=0,"",C84/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A84="",$J$12=0),"",C84/$J$12)</f>
         <v/>
       </c>
       <c r="F84" s="38">
-        <f>IF($A84="","",IF(C84&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C84&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A84="","",IF(C84&gt;=2*$J$12,"จุดหนืด",IF(C84&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H84">
@@ -11127,11 +11223,11 @@
         <v/>
       </c>
       <c r="E85" s="39">
-        <f>IF($A85="","",IF(MEDIAN($C$2:$C$152)=0,"",C85/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A85="",$J$12=0),"",C85/$J$12)</f>
         <v/>
       </c>
       <c r="F85" s="38">
-        <f>IF($A85="","",IF(C85&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C85&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A85="","",IF(C85&gt;=2*$J$12,"จุดหนืด",IF(C85&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H85">
@@ -11161,11 +11257,11 @@
         <v/>
       </c>
       <c r="E86" s="39">
-        <f>IF($A86="","",IF(MEDIAN($C$2:$C$152)=0,"",C86/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A86="",$J$12=0),"",C86/$J$12)</f>
         <v/>
       </c>
       <c r="F86" s="38">
-        <f>IF($A86="","",IF(C86&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C86&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A86="","",IF(C86&gt;=2*$J$12,"จุดหนืด",IF(C86&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H86">
@@ -11195,11 +11291,11 @@
         <v/>
       </c>
       <c r="E87" s="39">
-        <f>IF($A87="","",IF(MEDIAN($C$2:$C$152)=0,"",C87/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A87="",$J$12=0),"",C87/$J$12)</f>
         <v/>
       </c>
       <c r="F87" s="38">
-        <f>IF($A87="","",IF(C87&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C87&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A87="","",IF(C87&gt;=2*$J$12,"จุดหนืด",IF(C87&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H87">
@@ -11229,11 +11325,11 @@
         <v/>
       </c>
       <c r="E88" s="39">
-        <f>IF($A88="","",IF(MEDIAN($C$2:$C$152)=0,"",C88/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A88="",$J$12=0),"",C88/$J$12)</f>
         <v/>
       </c>
       <c r="F88" s="38">
-        <f>IF($A88="","",IF(C88&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C88&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A88="","",IF(C88&gt;=2*$J$12,"จุดหนืด",IF(C88&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H88">
@@ -11263,11 +11359,11 @@
         <v/>
       </c>
       <c r="E89" s="39">
-        <f>IF($A89="","",IF(MEDIAN($C$2:$C$152)=0,"",C89/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A89="",$J$12=0),"",C89/$J$12)</f>
         <v/>
       </c>
       <c r="F89" s="38">
-        <f>IF($A89="","",IF(C89&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C89&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A89="","",IF(C89&gt;=2*$J$12,"จุดหนืด",IF(C89&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H89">
@@ -11297,11 +11393,11 @@
         <v/>
       </c>
       <c r="E90" s="39">
-        <f>IF($A90="","",IF(MEDIAN($C$2:$C$152)=0,"",C90/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A90="",$J$12=0),"",C90/$J$12)</f>
         <v/>
       </c>
       <c r="F90" s="38">
-        <f>IF($A90="","",IF(C90&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C90&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A90="","",IF(C90&gt;=2*$J$12,"จุดหนืด",IF(C90&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H90">
@@ -11331,11 +11427,11 @@
         <v/>
       </c>
       <c r="E91" s="39">
-        <f>IF($A91="","",IF(MEDIAN($C$2:$C$152)=0,"",C91/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A91="",$J$12=0),"",C91/$J$12)</f>
         <v/>
       </c>
       <c r="F91" s="38">
-        <f>IF($A91="","",IF(C91&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C91&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A91="","",IF(C91&gt;=2*$J$12,"จุดหนืด",IF(C91&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H91">
@@ -11365,11 +11461,11 @@
         <v/>
       </c>
       <c r="E92" s="39">
-        <f>IF($A92="","",IF(MEDIAN($C$2:$C$152)=0,"",C92/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A92="",$J$12=0),"",C92/$J$12)</f>
         <v/>
       </c>
       <c r="F92" s="38">
-        <f>IF($A92="","",IF(C92&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C92&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A92="","",IF(C92&gt;=2*$J$12,"จุดหนืด",IF(C92&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H92">
@@ -11399,11 +11495,11 @@
         <v/>
       </c>
       <c r="E93" s="39">
-        <f>IF($A93="","",IF(MEDIAN($C$2:$C$152)=0,"",C93/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A93="",$J$12=0),"",C93/$J$12)</f>
         <v/>
       </c>
       <c r="F93" s="38">
-        <f>IF($A93="","",IF(C93&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C93&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A93="","",IF(C93&gt;=2*$J$12,"จุดหนืด",IF(C93&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H93">
@@ -11433,11 +11529,11 @@
         <v/>
       </c>
       <c r="E94" s="39">
-        <f>IF($A94="","",IF(MEDIAN($C$2:$C$152)=0,"",C94/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A94="",$J$12=0),"",C94/$J$12)</f>
         <v/>
       </c>
       <c r="F94" s="38">
-        <f>IF($A94="","",IF(C94&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C94&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A94="","",IF(C94&gt;=2*$J$12,"จุดหนืด",IF(C94&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H94">
@@ -11467,11 +11563,11 @@
         <v/>
       </c>
       <c r="E95" s="39">
-        <f>IF($A95="","",IF(MEDIAN($C$2:$C$152)=0,"",C95/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A95="",$J$12=0),"",C95/$J$12)</f>
         <v/>
       </c>
       <c r="F95" s="38">
-        <f>IF($A95="","",IF(C95&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C95&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A95="","",IF(C95&gt;=2*$J$12,"จุดหนืด",IF(C95&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H95">
@@ -11501,11 +11597,11 @@
         <v/>
       </c>
       <c r="E96" s="39">
-        <f>IF($A96="","",IF(MEDIAN($C$2:$C$152)=0,"",C96/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A96="",$J$12=0),"",C96/$J$12)</f>
         <v/>
       </c>
       <c r="F96" s="38">
-        <f>IF($A96="","",IF(C96&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C96&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A96="","",IF(C96&gt;=2*$J$12,"จุดหนืด",IF(C96&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H96">
@@ -11535,11 +11631,11 @@
         <v/>
       </c>
       <c r="E97" s="39">
-        <f>IF($A97="","",IF(MEDIAN($C$2:$C$152)=0,"",C97/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A97="",$J$12=0),"",C97/$J$12)</f>
         <v/>
       </c>
       <c r="F97" s="38">
-        <f>IF($A97="","",IF(C97&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C97&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A97="","",IF(C97&gt;=2*$J$12,"จุดหนืด",IF(C97&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H97">
@@ -11569,11 +11665,11 @@
         <v/>
       </c>
       <c r="E98" s="39">
-        <f>IF($A98="","",IF(MEDIAN($C$2:$C$152)=0,"",C98/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A98="",$J$12=0),"",C98/$J$12)</f>
         <v/>
       </c>
       <c r="F98" s="38">
-        <f>IF($A98="","",IF(C98&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C98&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A98="","",IF(C98&gt;=2*$J$12,"จุดหนืด",IF(C98&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H98">
@@ -11603,11 +11699,11 @@
         <v/>
       </c>
       <c r="E99" s="39">
-        <f>IF($A99="","",IF(MEDIAN($C$2:$C$152)=0,"",C99/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A99="",$J$12=0),"",C99/$J$12)</f>
         <v/>
       </c>
       <c r="F99" s="38">
-        <f>IF($A99="","",IF(C99&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C99&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A99="","",IF(C99&gt;=2*$J$12,"จุดหนืด",IF(C99&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H99">
@@ -11637,11 +11733,11 @@
         <v/>
       </c>
       <c r="E100" s="39">
-        <f>IF($A100="","",IF(MEDIAN($C$2:$C$152)=0,"",C100/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A100="",$J$12=0),"",C100/$J$12)</f>
         <v/>
       </c>
       <c r="F100" s="38">
-        <f>IF($A100="","",IF(C100&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C100&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A100="","",IF(C100&gt;=2*$J$12,"จุดหนืด",IF(C100&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H100">
@@ -11671,11 +11767,11 @@
         <v/>
       </c>
       <c r="E101" s="39">
-        <f>IF($A101="","",IF(MEDIAN($C$2:$C$152)=0,"",C101/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A101="",$J$12=0),"",C101/$J$12)</f>
         <v/>
       </c>
       <c r="F101" s="38">
-        <f>IF($A101="","",IF(C101&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C101&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A101="","",IF(C101&gt;=2*$J$12,"จุดหนืด",IF(C101&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H101">
@@ -11705,11 +11801,11 @@
         <v/>
       </c>
       <c r="E102" s="39">
-        <f>IF($A102="","",IF(MEDIAN($C$2:$C$152)=0,"",C102/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A102="",$J$12=0),"",C102/$J$12)</f>
         <v/>
       </c>
       <c r="F102" s="38">
-        <f>IF($A102="","",IF(C102&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C102&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A102="","",IF(C102&gt;=2*$J$12,"จุดหนืด",IF(C102&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H102">
@@ -11739,11 +11835,11 @@
         <v/>
       </c>
       <c r="E103" s="39">
-        <f>IF($A103="","",IF(MEDIAN($C$2:$C$152)=0,"",C103/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A103="",$J$12=0),"",C103/$J$12)</f>
         <v/>
       </c>
       <c r="F103" s="38">
-        <f>IF($A103="","",IF(C103&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C103&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A103="","",IF(C103&gt;=2*$J$12,"จุดหนืด",IF(C103&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H103">
@@ -11773,11 +11869,11 @@
         <v/>
       </c>
       <c r="E104" s="39">
-        <f>IF($A104="","",IF(MEDIAN($C$2:$C$152)=0,"",C104/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A104="",$J$12=0),"",C104/$J$12)</f>
         <v/>
       </c>
       <c r="F104" s="38">
-        <f>IF($A104="","",IF(C104&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C104&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A104="","",IF(C104&gt;=2*$J$12,"จุดหนืด",IF(C104&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H104">
@@ -11807,11 +11903,11 @@
         <v/>
       </c>
       <c r="E105" s="39">
-        <f>IF($A105="","",IF(MEDIAN($C$2:$C$152)=0,"",C105/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A105="",$J$12=0),"",C105/$J$12)</f>
         <v/>
       </c>
       <c r="F105" s="38">
-        <f>IF($A105="","",IF(C105&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C105&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A105="","",IF(C105&gt;=2*$J$12,"จุดหนืด",IF(C105&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H105">
@@ -11841,11 +11937,11 @@
         <v/>
       </c>
       <c r="E106" s="39">
-        <f>IF($A106="","",IF(MEDIAN($C$2:$C$152)=0,"",C106/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A106="",$J$12=0),"",C106/$J$12)</f>
         <v/>
       </c>
       <c r="F106" s="38">
-        <f>IF($A106="","",IF(C106&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C106&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A106="","",IF(C106&gt;=2*$J$12,"จุดหนืด",IF(C106&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H106">
@@ -11875,11 +11971,11 @@
         <v/>
       </c>
       <c r="E107" s="39">
-        <f>IF($A107="","",IF(MEDIAN($C$2:$C$152)=0,"",C107/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A107="",$J$12=0),"",C107/$J$12)</f>
         <v/>
       </c>
       <c r="F107" s="38">
-        <f>IF($A107="","",IF(C107&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C107&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A107="","",IF(C107&gt;=2*$J$12,"จุดหนืด",IF(C107&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H107">
@@ -11909,11 +12005,11 @@
         <v/>
       </c>
       <c r="E108" s="39">
-        <f>IF($A108="","",IF(MEDIAN($C$2:$C$152)=0,"",C108/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A108="",$J$12=0),"",C108/$J$12)</f>
         <v/>
       </c>
       <c r="F108" s="38">
-        <f>IF($A108="","",IF(C108&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C108&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A108="","",IF(C108&gt;=2*$J$12,"จุดหนืด",IF(C108&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H108">
@@ -11943,11 +12039,11 @@
         <v/>
       </c>
       <c r="E109" s="39">
-        <f>IF($A109="","",IF(MEDIAN($C$2:$C$152)=0,"",C109/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A109="",$J$12=0),"",C109/$J$12)</f>
         <v/>
       </c>
       <c r="F109" s="38">
-        <f>IF($A109="","",IF(C109&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C109&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A109="","",IF(C109&gt;=2*$J$12,"จุดหนืด",IF(C109&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H109">
@@ -11977,11 +12073,11 @@
         <v/>
       </c>
       <c r="E110" s="39">
-        <f>IF($A110="","",IF(MEDIAN($C$2:$C$152)=0,"",C110/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A110="",$J$12=0),"",C110/$J$12)</f>
         <v/>
       </c>
       <c r="F110" s="38">
-        <f>IF($A110="","",IF(C110&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C110&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A110="","",IF(C110&gt;=2*$J$12,"จุดหนืด",IF(C110&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H110">
@@ -12011,11 +12107,11 @@
         <v/>
       </c>
       <c r="E111" s="39">
-        <f>IF($A111="","",IF(MEDIAN($C$2:$C$152)=0,"",C111/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A111="",$J$12=0),"",C111/$J$12)</f>
         <v/>
       </c>
       <c r="F111" s="38">
-        <f>IF($A111="","",IF(C111&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C111&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A111="","",IF(C111&gt;=2*$J$12,"จุดหนืด",IF(C111&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H111">
@@ -12045,11 +12141,11 @@
         <v/>
       </c>
       <c r="E112" s="39">
-        <f>IF($A112="","",IF(MEDIAN($C$2:$C$152)=0,"",C112/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A112="",$J$12=0),"",C112/$J$12)</f>
         <v/>
       </c>
       <c r="F112" s="38">
-        <f>IF($A112="","",IF(C112&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C112&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A112="","",IF(C112&gt;=2*$J$12,"จุดหนืด",IF(C112&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H112">
@@ -12079,11 +12175,11 @@
         <v/>
       </c>
       <c r="E113" s="39">
-        <f>IF($A113="","",IF(MEDIAN($C$2:$C$152)=0,"",C113/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A113="",$J$12=0),"",C113/$J$12)</f>
         <v/>
       </c>
       <c r="F113" s="38">
-        <f>IF($A113="","",IF(C113&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C113&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A113="","",IF(C113&gt;=2*$J$12,"จุดหนืด",IF(C113&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H113">
@@ -12113,11 +12209,11 @@
         <v/>
       </c>
       <c r="E114" s="39">
-        <f>IF($A114="","",IF(MEDIAN($C$2:$C$152)=0,"",C114/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A114="",$J$12=0),"",C114/$J$12)</f>
         <v/>
       </c>
       <c r="F114" s="38">
-        <f>IF($A114="","",IF(C114&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C114&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A114="","",IF(C114&gt;=2*$J$12,"จุดหนืด",IF(C114&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H114">
@@ -12147,11 +12243,11 @@
         <v/>
       </c>
       <c r="E115" s="39">
-        <f>IF($A115="","",IF(MEDIAN($C$2:$C$152)=0,"",C115/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A115="",$J$12=0),"",C115/$J$12)</f>
         <v/>
       </c>
       <c r="F115" s="38">
-        <f>IF($A115="","",IF(C115&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C115&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A115="","",IF(C115&gt;=2*$J$12,"จุดหนืด",IF(C115&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H115">
@@ -12181,11 +12277,11 @@
         <v/>
       </c>
       <c r="E116" s="39">
-        <f>IF($A116="","",IF(MEDIAN($C$2:$C$152)=0,"",C116/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A116="",$J$12=0),"",C116/$J$12)</f>
         <v/>
       </c>
       <c r="F116" s="38">
-        <f>IF($A116="","",IF(C116&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C116&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A116="","",IF(C116&gt;=2*$J$12,"จุดหนืด",IF(C116&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H116">
@@ -12215,11 +12311,11 @@
         <v/>
       </c>
       <c r="E117" s="39">
-        <f>IF($A117="","",IF(MEDIAN($C$2:$C$152)=0,"",C117/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A117="",$J$12=0),"",C117/$J$12)</f>
         <v/>
       </c>
       <c r="F117" s="38">
-        <f>IF($A117="","",IF(C117&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C117&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A117="","",IF(C117&gt;=2*$J$12,"จุดหนืด",IF(C117&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H117">
@@ -12249,11 +12345,11 @@
         <v/>
       </c>
       <c r="E118" s="39">
-        <f>IF($A118="","",IF(MEDIAN($C$2:$C$152)=0,"",C118/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A118="",$J$12=0),"",C118/$J$12)</f>
         <v/>
       </c>
       <c r="F118" s="38">
-        <f>IF($A118="","",IF(C118&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C118&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A118="","",IF(C118&gt;=2*$J$12,"จุดหนืด",IF(C118&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H118">
@@ -12283,11 +12379,11 @@
         <v/>
       </c>
       <c r="E119" s="39">
-        <f>IF($A119="","",IF(MEDIAN($C$2:$C$152)=0,"",C119/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A119="",$J$12=0),"",C119/$J$12)</f>
         <v/>
       </c>
       <c r="F119" s="38">
-        <f>IF($A119="","",IF(C119&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C119&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A119="","",IF(C119&gt;=2*$J$12,"จุดหนืด",IF(C119&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H119">
@@ -12317,11 +12413,11 @@
         <v/>
       </c>
       <c r="E120" s="39">
-        <f>IF($A120="","",IF(MEDIAN($C$2:$C$152)=0,"",C120/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A120="",$J$12=0),"",C120/$J$12)</f>
         <v/>
       </c>
       <c r="F120" s="38">
-        <f>IF($A120="","",IF(C120&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C120&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A120="","",IF(C120&gt;=2*$J$12,"จุดหนืด",IF(C120&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H120">
@@ -12351,11 +12447,11 @@
         <v/>
       </c>
       <c r="E121" s="39">
-        <f>IF($A121="","",IF(MEDIAN($C$2:$C$152)=0,"",C121/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A121="",$J$12=0),"",C121/$J$12)</f>
         <v/>
       </c>
       <c r="F121" s="38">
-        <f>IF($A121="","",IF(C121&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C121&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A121="","",IF(C121&gt;=2*$J$12,"จุดหนืด",IF(C121&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H121">
@@ -12385,11 +12481,11 @@
         <v/>
       </c>
       <c r="E122" s="39">
-        <f>IF($A122="","",IF(MEDIAN($C$2:$C$152)=0,"",C122/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A122="",$J$12=0),"",C122/$J$12)</f>
         <v/>
       </c>
       <c r="F122" s="38">
-        <f>IF($A122="","",IF(C122&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C122&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A122="","",IF(C122&gt;=2*$J$12,"จุดหนืด",IF(C122&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H122">
@@ -12419,11 +12515,11 @@
         <v/>
       </c>
       <c r="E123" s="39">
-        <f>IF($A123="","",IF(MEDIAN($C$2:$C$152)=0,"",C123/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A123="",$J$12=0),"",C123/$J$12)</f>
         <v/>
       </c>
       <c r="F123" s="38">
-        <f>IF($A123="","",IF(C123&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C123&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A123="","",IF(C123&gt;=2*$J$12,"จุดหนืด",IF(C123&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H123">
@@ -12453,11 +12549,11 @@
         <v/>
       </c>
       <c r="E124" s="39">
-        <f>IF($A124="","",IF(MEDIAN($C$2:$C$152)=0,"",C124/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A124="",$J$12=0),"",C124/$J$12)</f>
         <v/>
       </c>
       <c r="F124" s="38">
-        <f>IF($A124="","",IF(C124&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C124&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A124="","",IF(C124&gt;=2*$J$12,"จุดหนืด",IF(C124&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H124">
@@ -12487,11 +12583,11 @@
         <v/>
       </c>
       <c r="E125" s="39">
-        <f>IF($A125="","",IF(MEDIAN($C$2:$C$152)=0,"",C125/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A125="",$J$12=0),"",C125/$J$12)</f>
         <v/>
       </c>
       <c r="F125" s="38">
-        <f>IF($A125="","",IF(C125&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C125&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A125="","",IF(C125&gt;=2*$J$12,"จุดหนืด",IF(C125&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H125">
@@ -12521,11 +12617,11 @@
         <v/>
       </c>
       <c r="E126" s="39">
-        <f>IF($A126="","",IF(MEDIAN($C$2:$C$152)=0,"",C126/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A126="",$J$12=0),"",C126/$J$12)</f>
         <v/>
       </c>
       <c r="F126" s="38">
-        <f>IF($A126="","",IF(C126&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C126&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A126="","",IF(C126&gt;=2*$J$12,"จุดหนืด",IF(C126&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H126">
@@ -12555,11 +12651,11 @@
         <v/>
       </c>
       <c r="E127" s="39">
-        <f>IF($A127="","",IF(MEDIAN($C$2:$C$152)=0,"",C127/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A127="",$J$12=0),"",C127/$J$12)</f>
         <v/>
       </c>
       <c r="F127" s="38">
-        <f>IF($A127="","",IF(C127&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C127&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A127="","",IF(C127&gt;=2*$J$12,"จุดหนืด",IF(C127&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H127">
@@ -12589,11 +12685,11 @@
         <v/>
       </c>
       <c r="E128" s="39">
-        <f>IF($A128="","",IF(MEDIAN($C$2:$C$152)=0,"",C128/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A128="",$J$12=0),"",C128/$J$12)</f>
         <v/>
       </c>
       <c r="F128" s="38">
-        <f>IF($A128="","",IF(C128&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C128&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A128="","",IF(C128&gt;=2*$J$12,"จุดหนืด",IF(C128&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H128">
@@ -12623,11 +12719,11 @@
         <v/>
       </c>
       <c r="E129" s="39">
-        <f>IF($A129="","",IF(MEDIAN($C$2:$C$152)=0,"",C129/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A129="",$J$12=0),"",C129/$J$12)</f>
         <v/>
       </c>
       <c r="F129" s="38">
-        <f>IF($A129="","",IF(C129&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C129&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A129="","",IF(C129&gt;=2*$J$12,"จุดหนืด",IF(C129&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H129">
@@ -12657,11 +12753,11 @@
         <v/>
       </c>
       <c r="E130" s="39">
-        <f>IF($A130="","",IF(MEDIAN($C$2:$C$152)=0,"",C130/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A130="",$J$12=0),"",C130/$J$12)</f>
         <v/>
       </c>
       <c r="F130" s="38">
-        <f>IF($A130="","",IF(C130&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C130&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A130="","",IF(C130&gt;=2*$J$12,"จุดหนืด",IF(C130&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H130">
@@ -12691,11 +12787,11 @@
         <v/>
       </c>
       <c r="E131" s="39">
-        <f>IF($A131="","",IF(MEDIAN($C$2:$C$152)=0,"",C131/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A131="",$J$12=0),"",C131/$J$12)</f>
         <v/>
       </c>
       <c r="F131" s="38">
-        <f>IF($A131="","",IF(C131&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C131&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A131="","",IF(C131&gt;=2*$J$12,"จุดหนืด",IF(C131&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H131">
@@ -12725,11 +12821,11 @@
         <v/>
       </c>
       <c r="E132" s="39">
-        <f>IF($A132="","",IF(MEDIAN($C$2:$C$152)=0,"",C132/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A132="",$J$12=0),"",C132/$J$12)</f>
         <v/>
       </c>
       <c r="F132" s="38">
-        <f>IF($A132="","",IF(C132&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C132&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A132="","",IF(C132&gt;=2*$J$12,"จุดหนืด",IF(C132&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H132">
@@ -12759,11 +12855,11 @@
         <v/>
       </c>
       <c r="E133" s="39">
-        <f>IF($A133="","",IF(MEDIAN($C$2:$C$152)=0,"",C133/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A133="",$J$12=0),"",C133/$J$12)</f>
         <v/>
       </c>
       <c r="F133" s="38">
-        <f>IF($A133="","",IF(C133&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C133&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A133="","",IF(C133&gt;=2*$J$12,"จุดหนืด",IF(C133&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H133">
@@ -12793,11 +12889,11 @@
         <v/>
       </c>
       <c r="E134" s="39">
-        <f>IF($A134="","",IF(MEDIAN($C$2:$C$152)=0,"",C134/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A134="",$J$12=0),"",C134/$J$12)</f>
         <v/>
       </c>
       <c r="F134" s="38">
-        <f>IF($A134="","",IF(C134&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C134&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A134="","",IF(C134&gt;=2*$J$12,"จุดหนืด",IF(C134&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H134">
@@ -12827,11 +12923,11 @@
         <v/>
       </c>
       <c r="E135" s="39">
-        <f>IF($A135="","",IF(MEDIAN($C$2:$C$152)=0,"",C135/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A135="",$J$12=0),"",C135/$J$12)</f>
         <v/>
       </c>
       <c r="F135" s="38">
-        <f>IF($A135="","",IF(C135&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C135&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A135="","",IF(C135&gt;=2*$J$12,"จุดหนืด",IF(C135&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H135">
@@ -12861,11 +12957,11 @@
         <v/>
       </c>
       <c r="E136" s="39">
-        <f>IF($A136="","",IF(MEDIAN($C$2:$C$152)=0,"",C136/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A136="",$J$12=0),"",C136/$J$12)</f>
         <v/>
       </c>
       <c r="F136" s="38">
-        <f>IF($A136="","",IF(C136&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C136&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A136="","",IF(C136&gt;=2*$J$12,"จุดหนืด",IF(C136&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H136">
@@ -12895,11 +12991,11 @@
         <v/>
       </c>
       <c r="E137" s="39">
-        <f>IF($A137="","",IF(MEDIAN($C$2:$C$152)=0,"",C137/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A137="",$J$12=0),"",C137/$J$12)</f>
         <v/>
       </c>
       <c r="F137" s="38">
-        <f>IF($A137="","",IF(C137&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C137&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A137="","",IF(C137&gt;=2*$J$12,"จุดหนืด",IF(C137&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H137">
@@ -12929,11 +13025,11 @@
         <v/>
       </c>
       <c r="E138" s="39">
-        <f>IF($A138="","",IF(MEDIAN($C$2:$C$152)=0,"",C138/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A138="",$J$12=0),"",C138/$J$12)</f>
         <v/>
       </c>
       <c r="F138" s="38">
-        <f>IF($A138="","",IF(C138&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C138&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A138="","",IF(C138&gt;=2*$J$12,"จุดหนืด",IF(C138&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H138">
@@ -12963,11 +13059,11 @@
         <v/>
       </c>
       <c r="E139" s="39">
-        <f>IF($A139="","",IF(MEDIAN($C$2:$C$152)=0,"",C139/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A139="",$J$12=0),"",C139/$J$12)</f>
         <v/>
       </c>
       <c r="F139" s="38">
-        <f>IF($A139="","",IF(C139&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C139&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A139="","",IF(C139&gt;=2*$J$12,"จุดหนืด",IF(C139&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H139">
@@ -12997,11 +13093,11 @@
         <v/>
       </c>
       <c r="E140" s="39">
-        <f>IF($A140="","",IF(MEDIAN($C$2:$C$152)=0,"",C140/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A140="",$J$12=0),"",C140/$J$12)</f>
         <v/>
       </c>
       <c r="F140" s="38">
-        <f>IF($A140="","",IF(C140&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C140&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A140="","",IF(C140&gt;=2*$J$12,"จุดหนืด",IF(C140&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H140">
@@ -13031,11 +13127,11 @@
         <v/>
       </c>
       <c r="E141" s="39">
-        <f>IF($A141="","",IF(MEDIAN($C$2:$C$152)=0,"",C141/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A141="",$J$12=0),"",C141/$J$12)</f>
         <v/>
       </c>
       <c r="F141" s="38">
-        <f>IF($A141="","",IF(C141&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C141&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A141="","",IF(C141&gt;=2*$J$12,"จุดหนืด",IF(C141&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H141">
@@ -13065,11 +13161,11 @@
         <v/>
       </c>
       <c r="E142" s="39">
-        <f>IF($A142="","",IF(MEDIAN($C$2:$C$152)=0,"",C142/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A142="",$J$12=0),"",C142/$J$12)</f>
         <v/>
       </c>
       <c r="F142" s="38">
-        <f>IF($A142="","",IF(C142&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C142&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A142="","",IF(C142&gt;=2*$J$12,"จุดหนืด",IF(C142&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H142">
@@ -13099,11 +13195,11 @@
         <v/>
       </c>
       <c r="E143" s="39">
-        <f>IF($A143="","",IF(MEDIAN($C$2:$C$152)=0,"",C143/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A143="",$J$12=0),"",C143/$J$12)</f>
         <v/>
       </c>
       <c r="F143" s="38">
-        <f>IF($A143="","",IF(C143&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C143&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A143="","",IF(C143&gt;=2*$J$12,"จุดหนืด",IF(C143&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H143">
@@ -13133,11 +13229,11 @@
         <v/>
       </c>
       <c r="E144" s="39">
-        <f>IF($A144="","",IF(MEDIAN($C$2:$C$152)=0,"",C144/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A144="",$J$12=0),"",C144/$J$12)</f>
         <v/>
       </c>
       <c r="F144" s="38">
-        <f>IF($A144="","",IF(C144&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C144&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A144="","",IF(C144&gt;=2*$J$12,"จุดหนืด",IF(C144&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H144">
@@ -13167,11 +13263,11 @@
         <v/>
       </c>
       <c r="E145" s="39">
-        <f>IF($A145="","",IF(MEDIAN($C$2:$C$152)=0,"",C145/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A145="",$J$12=0),"",C145/$J$12)</f>
         <v/>
       </c>
       <c r="F145" s="38">
-        <f>IF($A145="","",IF(C145&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C145&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A145="","",IF(C145&gt;=2*$J$12,"จุดหนืด",IF(C145&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H145">
@@ -13201,11 +13297,11 @@
         <v/>
       </c>
       <c r="E146" s="39">
-        <f>IF($A146="","",IF(MEDIAN($C$2:$C$152)=0,"",C146/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A146="",$J$12=0),"",C146/$J$12)</f>
         <v/>
       </c>
       <c r="F146" s="38">
-        <f>IF($A146="","",IF(C146&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C146&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A146="","",IF(C146&gt;=2*$J$12,"จุดหนืด",IF(C146&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H146">
@@ -13235,11 +13331,11 @@
         <v/>
       </c>
       <c r="E147" s="39">
-        <f>IF($A147="","",IF(MEDIAN($C$2:$C$152)=0,"",C147/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A147="",$J$12=0),"",C147/$J$12)</f>
         <v/>
       </c>
       <c r="F147" s="38">
-        <f>IF($A147="","",IF(C147&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C147&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A147="","",IF(C147&gt;=2*$J$12,"จุดหนืด",IF(C147&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H147">
@@ -13269,11 +13365,11 @@
         <v/>
       </c>
       <c r="E148" s="39">
-        <f>IF($A148="","",IF(MEDIAN($C$2:$C$152)=0,"",C148/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A148="",$J$12=0),"",C148/$J$12)</f>
         <v/>
       </c>
       <c r="F148" s="38">
-        <f>IF($A148="","",IF(C148&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C148&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A148="","",IF(C148&gt;=2*$J$12,"จุดหนืด",IF(C148&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H148">
@@ -13303,11 +13399,11 @@
         <v/>
       </c>
       <c r="E149" s="39">
-        <f>IF($A149="","",IF(MEDIAN($C$2:$C$152)=0,"",C149/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A149="",$J$12=0),"",C149/$J$12)</f>
         <v/>
       </c>
       <c r="F149" s="38">
-        <f>IF($A149="","",IF(C149&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C149&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A149="","",IF(C149&gt;=2*$J$12,"จุดหนืด",IF(C149&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H149">
@@ -13337,11 +13433,11 @@
         <v/>
       </c>
       <c r="E150" s="39">
-        <f>IF($A150="","",IF(MEDIAN($C$2:$C$152)=0,"",C150/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A150="",$J$12=0),"",C150/$J$12)</f>
         <v/>
       </c>
       <c r="F150" s="38">
-        <f>IF($A150="","",IF(C150&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C150&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A150="","",IF(C150&gt;=2*$J$12,"จุดหนืด",IF(C150&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H150">
@@ -13371,11 +13467,11 @@
         <v/>
       </c>
       <c r="E151" s="39">
-        <f>IF($A151="","",IF(MEDIAN($C$2:$C$152)=0,"",C151/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A151="",$J$12=0),"",C151/$J$12)</f>
         <v/>
       </c>
       <c r="F151" s="38">
-        <f>IF($A151="","",IF(C151&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C151&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A151="","",IF(C151&gt;=2*$J$12,"จุดหนืด",IF(C151&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H151">
@@ -13405,11 +13501,11 @@
         <v/>
       </c>
       <c r="E152" s="39">
-        <f>IF($A152="","",IF(MEDIAN($C$2:$C$152)=0,"",C152/MEDIAN($C$2:$C$152)))</f>
+        <f>IF(OR(A152="",$J$12=0),"",C152/$J$12)</f>
         <v/>
       </c>
       <c r="F152" s="38">
-        <f>IF($A152="","",IF(C152&gt;=2*MEDIAN($C$2:$C$152),"จุดหนืด",IF(C152&lt;=0.5*MEDIAN($C$2:$C$152),"air pocket","")))</f>
+        <f>IF(A152="","",IF(C152&gt;=2*$J$12,"จุดหนืด",IF(C152&lt;=0.5*$J$12,"air pocket","")))</f>
         <v/>
       </c>
       <c r="H152">
@@ -18098,7 +18194,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.42578125" bestFit="1" customWidth="1" style="61" min="1" max="1"/>
@@ -18373,6 +18469,52 @@
       </c>
       <c r="N6" s="32" t="n">
         <v>0.170028818443804</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>OG2V6</t>
+        </is>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>4212.2</v>
+      </c>
+      <c r="D7" s="29" t="n">
+        <v>396</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>647</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-251</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Negative GEX (วิ่ง)</t>
+        </is>
+      </c>
+      <c r="H7" s="29" t="n"/>
+      <c r="I7" s="29" t="n">
+        <v>4100</v>
+      </c>
+      <c r="J7" s="73" t="n">
+        <v>46304.50859695602</v>
+      </c>
+      <c r="K7" s="29" t="n">
+        <v>4250</v>
+      </c>
+      <c r="L7" s="29" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M7" s="29" t="n">
+        <v>4175</v>
+      </c>
+      <c r="N7" s="32" t="n">
+        <v>0.3414965986394558</v>
       </c>
     </row>
   </sheetData>
@@ -18386,7 +18528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18857,7 +18999,7 @@
         </is>
       </c>
       <c r="Q7" s="73" t="n">
-        <v>46298.65528628538</v>
+        <v>46298.65528628472</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -18925,7 +19067,7 @@
         </is>
       </c>
       <c r="Q8" s="73" t="n">
-        <v>46298.65528985655</v>
+        <v>46298.65528986111</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -18993,7 +19135,7 @@
         </is>
       </c>
       <c r="Q9" s="73" t="n">
-        <v>46298.65529687911</v>
+        <v>46298.655296875</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -19011,6 +19153,349 @@
       <c r="X9" s="29" t="n"/>
       <c r="Y9" s="29" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" s="71" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>MW1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="n">
+        <v>46300</v>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>4162.3</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>4215</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>-59</v>
+      </c>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="30" t="n">
+        <v>4156.8</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>4198.9</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>4150.4</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>52.69999999999982</v>
+      </c>
+      <c r="L10" s="30" t="n">
+        <v>58.19999999999982</v>
+      </c>
+      <c r="M10" s="30" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="N10" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="31" t="n">
+        <v>0.01165221151767052</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q10" s="73" t="n">
+        <v>46304.51002133097</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+      <c r="S10" s="30" t="n">
+        <v>4169.4</v>
+      </c>
+      <c r="T10" s="75" t="n">
+        <v>-40</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Negative GEX (วิ่ง)</t>
+        </is>
+      </c>
+      <c r="V10" s="32" t="n">
+        <v>0.170028818443804</v>
+      </c>
+      <c r="W10" s="29" t="n">
+        <v>4190</v>
+      </c>
+      <c r="X10" s="29" t="n">
+        <v>4150</v>
+      </c>
+      <c r="Y10" s="29" t="n">
+        <v>4190</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="71" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>AB1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="n">
+        <v>46301</v>
+      </c>
+      <c r="D11" s="30" t="n">
+        <v>4156.8</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>4185</v>
+      </c>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="30" t="n">
+        <v>4187.1</v>
+      </c>
+      <c r="I11" s="30" t="n">
+        <v>4212.4</v>
+      </c>
+      <c r="J11" s="30" t="n">
+        <v>4130.7</v>
+      </c>
+      <c r="K11" s="30" t="n">
+        <v>28.19999999999982</v>
+      </c>
+      <c r="L11" s="30" t="n">
+        <v>2.100000000000364</v>
+      </c>
+      <c r="M11" s="30" t="n">
+        <v>30.30000000000018</v>
+      </c>
+      <c r="N11" t="b">
+        <v>1</v>
+      </c>
+      <c r="O11" s="31" t="n">
+        <v>0.01965454195535022</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q11" s="73" t="n">
+        <v>46304.51002494697</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+      <c r="S11" s="30" t="n">
+        <v>4169.2</v>
+      </c>
+      <c r="T11" s="75" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="V11" s="32" t="n"/>
+      <c r="W11" s="29" t="n"/>
+      <c r="X11" s="29" t="n"/>
+      <c r="Y11" s="29" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>WD1 Week 1 - OCT 2026 (V26)</t>
+        </is>
+      </c>
+      <c r="C12" s="71" t="n">
+        <v>46302</v>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>4187.1</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>4200</v>
+      </c>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="30" t="n">
+        <v>4140.7</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>4197.8</v>
+      </c>
+      <c r="J12" s="30" t="n">
+        <v>4091.2</v>
+      </c>
+      <c r="K12" s="30" t="n">
+        <v>12.89999999999964</v>
+      </c>
+      <c r="L12" s="30" t="n">
+        <v>59.30000000000018</v>
+      </c>
+      <c r="M12" s="30" t="n">
+        <v>46.40000000000055</v>
+      </c>
+      <c r="N12" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="31" t="n">
+        <v>0.02545914833655761</v>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>1/1</t>
+        </is>
+      </c>
+      <c r="Q12" s="73" t="n">
+        <v>46304.51002865422</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>DEC 26</t>
+        </is>
+      </c>
+      <c r="S12" s="30" t="n">
+        <v>4195</v>
+      </c>
+      <c r="T12" s="75" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="V12" s="32" t="n"/>
+      <c r="W12" s="29" t="n"/>
+      <c r="X12" s="29" t="n"/>
+      <c r="Y12" s="29" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>วันที่ข้อมูล</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>สัญญาที่รวม</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ราคา</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>รวม Call Gamma</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>รวม Put Gamma</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>NET GEX</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>โหมด</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ความชัดเจน</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Call Wall</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Put Wall</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Gamma Flip</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Strike gamma สูงสุด</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>บันทึกเมื่อ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="71" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OG2V6, OGX6, OGZ6, OGF7, OGG7, OGH7, OGJ7, OGM7, OGQ7</t>
+        </is>
+      </c>
+      <c r="C2" s="30" t="n">
+        <v>4212.2</v>
+      </c>
+      <c r="D2" s="29" t="n">
+        <v>6849</v>
+      </c>
+      <c r="E2" s="29" t="n">
+        <v>7127</v>
+      </c>
+      <c r="F2" s="29" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ไม่มีโหมด</t>
+        </is>
+      </c>
+      <c r="H2" s="77" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="I2" s="29" t="n">
+        <v>4500</v>
+      </c>
+      <c r="J2" s="29" t="n">
+        <v>4000</v>
+      </c>
+      <c r="K2" s="29" t="n"/>
+      <c r="L2" s="29" t="n">
+        <v>4100</v>
+      </c>
+      <c r="M2" s="73" t="n">
+        <v>46304.50904158565</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
